--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Finished-Lot Model" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Phase 2 — Hospitality" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="161">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
@@ -260,6 +261,240 @@
   </si>
   <si>
     <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation in further conversations. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
+  </si>
+  <si>
+    <t>Queenstown Harbor — Phase 2: Hospitality (Hotel + Restaurants)</t>
+  </si>
+  <si>
+    <t>VIVAMEE-led resort; JAL as capital partner. Income / hold play — develops to ~cost; returns come from cash flow + appreciation.  ·  ILLUSTRATIVE.</t>
+  </si>
+  <si>
+    <t>Hotel — keys</t>
+  </si>
+  <si>
+    <t>boutique resort lodge</t>
+  </si>
+  <si>
+    <t>Hotel — cost / key ($)</t>
+  </si>
+  <si>
+    <t>HVS 2025: select ~$223K, full-service ~$409K</t>
+  </si>
+  <si>
+    <t>Hotel — ADR ($)</t>
+  </si>
+  <si>
+    <t>upscale Eastern Shore resort (weddings / golf)</t>
+  </si>
+  <si>
+    <t>Hotel — stabilized occupancy</t>
+  </si>
+  <si>
+    <t>leisure / resort</t>
+  </si>
+  <si>
+    <t>Hotel — total-revenue multiple (x rooms)</t>
+  </si>
+  <si>
+    <t>+ F&amp;B, banquets, spa</t>
+  </si>
+  <si>
+    <t>Hotel — NOI margin</t>
+  </si>
+  <si>
+    <t>stabilized</t>
+  </si>
+  <si>
+    <t>Restaurants — GLA (SF)</t>
+  </si>
+  <si>
+    <t>a suite of destination restaurants</t>
+  </si>
+  <si>
+    <t>Restaurants — build cost / SF ($)</t>
+  </si>
+  <si>
+    <t>full-service ~$555/SF</t>
+  </si>
+  <si>
+    <t>Restaurants — sales / SF ($)</t>
+  </si>
+  <si>
+    <t>upscale destination dining</t>
+  </si>
+  <si>
+    <t>Restaurants — NOI (% of sales)</t>
+  </si>
+  <si>
+    <t>rent / operating contribution</t>
+  </si>
+  <si>
+    <t>Land — hospitality parcel ($)</t>
+  </si>
+  <si>
+    <t>Soft / FF&amp;E / pre-opening ($)</t>
+  </si>
+  <si>
+    <t>Exit cap rate</t>
+  </si>
+  <si>
+    <t>hotel cap ~8% (2025)</t>
+  </si>
+  <si>
+    <t>Construction loan (% of cost)</t>
+  </si>
+  <si>
+    <t>Loan interest rate</t>
+  </si>
+  <si>
+    <t>NOI growth / yr</t>
+  </si>
+  <si>
+    <t>HOTEL</t>
+  </si>
+  <si>
+    <t>Hotel development cost</t>
+  </si>
+  <si>
+    <t>keys x cost/key</t>
+  </si>
+  <si>
+    <t>Room revenue</t>
+  </si>
+  <si>
+    <t>keys x 365 x ADR x occ</t>
+  </si>
+  <si>
+    <t>Total hotel revenue</t>
+  </si>
+  <si>
+    <t>x revenue multiple</t>
+  </si>
+  <si>
+    <t>Hotel NOI (stabilized)</t>
+  </si>
+  <si>
+    <t>x NOI margin</t>
+  </si>
+  <si>
+    <t>RESTAURANTS  (a suite of nice restaurants)</t>
+  </si>
+  <si>
+    <t>Restaurant development cost</t>
+  </si>
+  <si>
+    <t>SF x cost/SF</t>
+  </si>
+  <si>
+    <t>Restaurant sales</t>
+  </si>
+  <si>
+    <t>SF x sales/SF</t>
+  </si>
+  <si>
+    <t>Restaurant NOI (to owner)</t>
+  </si>
+  <si>
+    <t>TOTAL PROJECT  -&gt;  STABILIZED</t>
+  </si>
+  <si>
+    <t>Total project cost</t>
+  </si>
+  <si>
+    <t>hotel + restaurants + land + soft</t>
+  </si>
+  <si>
+    <t>Stabilized NOI</t>
+  </si>
+  <si>
+    <t>hotel + restaurant NOI</t>
+  </si>
+  <si>
+    <t>Yield on cost</t>
+  </si>
+  <si>
+    <t>NOI / cost</t>
+  </si>
+  <si>
+    <t>Construction loan</t>
+  </si>
+  <si>
+    <t>% LTC</t>
+  </si>
+  <si>
+    <t>Equity (land + cash)</t>
+  </si>
+  <si>
+    <t>cost - loan</t>
+  </si>
+  <si>
+    <t>Cash-on-cash (stabilized, levered)</t>
+  </si>
+  <si>
+    <t>(NOI - interest) / equity</t>
+  </si>
+  <si>
+    <t>EXIT  &amp;  RETURNS  (7-year hold)</t>
+  </si>
+  <si>
+    <t>Year-7 NOI (3%/yr growth)</t>
+  </si>
+  <si>
+    <t>stabilized x growth</t>
+  </si>
+  <si>
+    <t>Exit value (@ exit cap)</t>
+  </si>
+  <si>
+    <t>Year-7 NOI / cap</t>
+  </si>
+  <si>
+    <t>Exit equity (value - loan)</t>
+  </si>
+  <si>
+    <t>net of loan</t>
+  </si>
+  <si>
+    <t>EQUITY CASH FLOW (levered, $) &amp; RETURNS</t>
+  </si>
+  <si>
+    <t>Year 0</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Year 6</t>
+  </si>
+  <si>
+    <t>Year 7</t>
+  </si>
+  <si>
+    <t>Equity multiple (7-yr)</t>
+  </si>
+  <si>
+    <t>distributions / equity</t>
+  </si>
+  <si>
+    <t>Project IRR (levered, 7-yr)</t>
+  </si>
+  <si>
+    <t>equity cash flows Yr 0–7</t>
+  </si>
+  <si>
+    <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold). VIVAMEE operates; JAL is the capital partner (debt + equity placement fees, co-invest, promote). The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
   </si>
 </sst>
 </file>
@@ -272,7 +507,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -354,6 +589,17 @@
       <color rgb="FF6B5A6B"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <color rgb="FF0B163C"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B5A6B"/>
+      <sz val="8.5"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -390,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -450,6 +696,18 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1464,4 +1722,679 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="7">
+        <v>100</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="10">
+        <v>325000</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="10">
+        <v>250</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.62</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="25">
+        <v>1.6</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="7">
+        <v>16000</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="10">
+        <v>550</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="10">
+        <v>700</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10">
+        <v>3700000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="11">
+        <v>0.08</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="11">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="11">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="11">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="10">
+        <f>B5*B6</f>
+        <v>32500000</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="10">
+        <f>B5*365*B7*B8</f>
+        <v>5657500</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="10">
+        <f>B24*B9</f>
+        <v>9052000</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="14">
+        <f>B25*B10</f>
+        <v>2806120</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="10">
+        <f>B11*B12</f>
+        <v>8800000</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="10">
+        <f>B11*B13</f>
+        <v>11200000</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="14">
+        <f>B30*B14</f>
+        <v>1008000</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="16">
+        <f>B23+B29+B15+B16</f>
+        <v>47000000</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="16">
+        <f>B26+B31</f>
+        <v>3814120</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="11">
+        <f>B35/B34</f>
+        <v>0.0811</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="10">
+        <f>B34*B18</f>
+        <v>28200000</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="10">
+        <f>B34-B37</f>
+        <v>18800000</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" s="11">
+        <f>(B35-B37*B19)/B38</f>
+        <v>0.098</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" s="10">
+        <f>B35*(1+B20)^4</f>
+        <v>4292800</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="10">
+        <f>B42/B17</f>
+        <v>53660000</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" s="10">
+        <f>B43-B37</f>
+        <v>25460000</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="26">
+        <v>-9400000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="26">
+        <v>-9400000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="26">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="26">
+        <v>1840000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="26">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="26">
+        <v>1950000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="26">
+        <v>2010000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="26">
+        <v>27530000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="17">
+        <f>SUM(B49:B54)/-(B47+B48)</f>
+        <v>1.9218085106382978</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" s="27">
+        <f>IRR(B47:B54)</f>
+        <v>0.12022015409362574</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+    </row>
+    <row r="58" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="A58:F58"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="187">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
@@ -260,6 +260,18 @@
     <t>entitlement/land Yr 0–1, horizontal Yr 1–2, finished-lot sales Yr 2–4</t>
   </si>
   <si>
+    <t>LEVERED EQUITY RETURN  (~60% LTC development loan)</t>
+  </si>
+  <si>
+    <t>Equity cash flow (levered)</t>
+  </si>
+  <si>
+    <t>Equity IRR (levered, phased)</t>
+  </si>
+  <si>
+    <t>equity deployed Yr 0–1; lot sales Yr 2–4 (60% LTC). Unlevered project IRR ~24%.</t>
+  </si>
+  <si>
     <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation in further conversations. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
   </si>
   <si>
@@ -492,6 +504,72 @@
   </si>
   <si>
     <t>equity cash flows Yr 0–7</t>
+  </si>
+  <si>
+    <t>BUILD-TO-CORE CASE  (path to mid–high 20s IRR — recap / sell at stabilization)</t>
+  </si>
+  <si>
+    <t>NOI uplift — premium execution</t>
+  </si>
+  <si>
+    <t>VIVAMEE experiential: ADR ~$275, occ ~63%, strong F&amp;B / events</t>
+  </si>
+  <si>
+    <t>Premium stabilized NOI</t>
+  </si>
+  <si>
+    <t>base NOI x (1 + uplift)</t>
+  </si>
+  <si>
+    <t>Exit cap (build-to-core)</t>
+  </si>
+  <si>
+    <t>trophy / experiential resort</t>
+  </si>
+  <si>
+    <t>Leverage (% of cost)</t>
+  </si>
+  <si>
+    <t>construction loan</t>
+  </si>
+  <si>
+    <t>Yield on cost (premium)</t>
+  </si>
+  <si>
+    <t>premium NOI / cost — vs 7.5% exit = the spread</t>
+  </si>
+  <si>
+    <t>Recap / sale value (~Yr 4)</t>
+  </si>
+  <si>
+    <t>premium NOI / exit cap</t>
+  </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
+    <t>% of cost</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>at recap / sale</t>
+  </si>
+  <si>
+    <t>BUILD-TO-CORE EQUITY CASH FLOW (Yr 0–4, $) &amp; RETURNS</t>
+  </si>
+  <si>
+    <t>Equity multiple (build-to-core)</t>
+  </si>
+  <si>
+    <t>distributions / equity, ~4-yr</t>
+  </si>
+  <si>
+    <t>Project IRR (build-to-core, ~4-yr)</t>
+  </si>
+  <si>
+    <t>recap / sell at stabilization</t>
   </si>
   <si>
     <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold). VIVAMEE operates; JAL is the capital partner (debt + equity placement fees, co-invest, promote). The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
@@ -1049,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1672,18 +1750,83 @@
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
     </row>
-    <row r="54" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56" s="20">
+        <v>-7000000</v>
+      </c>
+      <c r="C56" s="20">
+        <v>-4000000</v>
+      </c>
+      <c r="D56" s="20">
+        <v>3000000</v>
+      </c>
+      <c r="E56" s="20">
+        <v>9000000</v>
+      </c>
+      <c r="F56" s="20">
+        <v>13500000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" s="22">
+        <f>IRR(B56:F56)</f>
+        <v>0.32226911894673804</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+    </row>
+    <row r="59" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -1717,7 +1860,8 @@
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C52:F52"/>
-    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1726,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1737,7 +1881,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1747,7 +1891,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1767,13 +1911,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1781,13 +1925,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1795,13 +1939,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -1809,13 +1953,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -1823,13 +1967,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B9" s="25">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1837,13 +1981,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -1851,13 +1995,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -1865,13 +2009,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -1879,13 +2023,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -1893,13 +2037,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -1907,7 +2051,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
@@ -1921,7 +2065,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -1929,13 +2073,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -1943,7 +2087,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -1951,7 +2095,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -1959,7 +2103,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -1967,7 +2111,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1977,14 +2121,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B23" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1992,14 +2136,14 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B24" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -2007,14 +2151,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B25" s="10">
         <f>B24*B9</f>
         <v>9052000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2022,14 +2166,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B26" s="14">
         <f>B25*B10</f>
         <v>2806120</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2037,7 +2181,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2047,14 +2191,14 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B29" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -2062,14 +2206,14 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B30" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -2077,14 +2221,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B31" s="14">
         <f>B30*B14</f>
         <v>1008000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2092,7 +2236,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2102,14 +2246,14 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B34" s="16">
         <f>B23+B29+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -2117,14 +2261,14 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B35" s="16">
         <f>B26+B31</f>
         <v>3814120</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -2132,14 +2276,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B36" s="11">
         <f>B35/B34</f>
         <v>0.0811</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2147,14 +2291,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B37" s="10">
         <f>B34*B18</f>
         <v>28200000</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2162,14 +2306,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B38" s="10">
         <f>B34-B37</f>
         <v>18800000</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2177,14 +2321,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B39" s="11">
         <f>(B35-B37*B19)/B38</f>
         <v>0.098</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2192,7 +2336,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2202,14 +2346,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B42" s="10">
         <f>B35*(1+B20)^4</f>
         <v>4292800</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2217,14 +2361,14 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="10">
         <f>B42/B17</f>
         <v>53660000</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2232,14 +2376,14 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B44" s="10">
         <f>B43-B37</f>
         <v>25460000</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
@@ -2247,7 +2391,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2257,7 +2401,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B47" s="26">
         <v>-9400000</v>
@@ -2265,7 +2409,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B48" s="26">
         <v>-9400000</v>
@@ -2273,7 +2417,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B49" s="26">
         <v>900000</v>
@@ -2281,7 +2425,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B50" s="26">
         <v>1840000</v>
@@ -2289,7 +2433,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B51" s="26">
         <v>1900000</v>
@@ -2297,7 +2441,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B52" s="26">
         <v>1950000</v>
@@ -2305,7 +2449,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B53" s="26">
         <v>2010000</v>
@@ -2313,7 +2457,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B54" s="26">
         <v>27530000</v>
@@ -2321,14 +2465,14 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B49:B54)/-(B47+B48)</f>
         <v>1.9218085106382978</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -2336,31 +2480,253 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B56" s="27">
         <f>IRR(B47:B54)</f>
         <v>0.12022015409362574</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="58" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B60" s="14">
+        <f>B35*(1+B59)</f>
+        <v>4653226</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" s="11">
+        <v>0.075</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B63" s="11">
+        <f>B60/B34</f>
+        <v>0.099</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" s="10">
+        <f>B60/B61</f>
+        <v>62043015</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B65" s="10">
+        <f>B34*B62</f>
+        <v>30550000</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B66" s="10">
+        <f>B34-B65</f>
+        <v>16450000</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="10">
+        <f>B64-B65</f>
+        <v>31493015</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="26">
+        <v>-8225000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="26">
+        <v>-8225000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="26">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="26">
+        <v>2514726</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" s="26">
+        <v>34007741</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B75" s="17">
+        <f>SUM(B72:B74)/-(B70+B71)</f>
+        <v>2.2810010334346504</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76" s="27">
+        <f>IRR(B70:B74)</f>
+        <v>0.2755427433529377</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="78" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="43">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -2392,7 +2758,18 @@
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="C56:F56"/>
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="A78:F78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="196">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Development loan (% of total cost)</t>
   </si>
   <si>
-    <t>land-development / A&amp;D financing</t>
+    <t>land-development / A&amp;D financing (70% LTC)</t>
   </si>
   <si>
     <t>Preferred return</t>
@@ -260,16 +260,43 @@
     <t>entitlement/land Yr 0–1, horizontal Yr 1–2, finished-lot sales Yr 2–4</t>
   </si>
   <si>
-    <t>LEVERED EQUITY RETURN  (~60% LTC development loan)</t>
-  </si>
-  <si>
-    <t>Equity cash flow (levered)</t>
-  </si>
-  <si>
-    <t>Equity IRR (levered, phased)</t>
-  </si>
-  <si>
-    <t>equity deployed Yr 0–1; lot sales Yr 2–4 (60% LTC). Unlevered project IRR ~24%.</t>
+    <t>LEVERED EQUITY RETURN  (70% LTC development loan)</t>
+  </si>
+  <si>
+    <t>Project equity cash flow</t>
+  </si>
+  <si>
+    <t>Project equity IRR (levered)</t>
+  </si>
+  <si>
+    <t>equity ~$8.25M (70% LTC); lot sales Yr 2–4. Unlevered project IRR ~24%.</t>
+  </si>
+  <si>
+    <t>PROMOTE WATERFALL  (LP 90% / GP 10% · 8% pref · 80/20 to 15% · 70/30 to 20% · 60/40 above)</t>
+  </si>
+  <si>
+    <t>LP cash flow (after promote)</t>
+  </si>
+  <si>
+    <t>GP cash flow (co-invest + promote)</t>
+  </si>
+  <si>
+    <t>LP IRR (after promote)</t>
+  </si>
+  <si>
+    <t>what the equity investors earn</t>
+  </si>
+  <si>
+    <t>GP IRR (co-invest + carried interest)</t>
+  </si>
+  <si>
+    <t>JAL</t>
+  </si>
+  <si>
+    <t>GP net profit (co-invest + promote)</t>
+  </si>
+  <si>
+    <t>JAL's share of the upside</t>
   </si>
   <si>
     <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation in further conversations. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
@@ -773,6 +800,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -780,9 +810,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1127,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1339,7 +1366,7 @@
         <v>27</v>
       </c>
       <c r="B17" s="11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>28</v>
@@ -1785,19 +1812,19 @@
         <v>83</v>
       </c>
       <c r="B56" s="20">
-        <v>-7000000</v>
+        <v>-5000000</v>
       </c>
       <c r="C56" s="20">
-        <v>-4000000</v>
+        <v>-3231000</v>
       </c>
       <c r="D56" s="20">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="E56" s="20">
-        <v>9000000</v>
+        <v>7000000</v>
       </c>
       <c r="F56" s="20">
-        <v>13500000</v>
+        <v>13795000</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,7 +1833,7 @@
       </c>
       <c r="B57" s="22">
         <f>IRR(B56:F56)</f>
-        <v>0.32226911894673804</v>
+        <v>0.39078273593623514</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>85</v>
@@ -1815,18 +1842,113 @@
       <c r="E57" s="23"/>
       <c r="F57" s="23"/>
     </row>
-    <row r="59" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="20">
+        <v>-4500000</v>
+      </c>
+      <c r="C60" s="20">
+        <v>-2907900</v>
+      </c>
+      <c r="D60" s="20">
+        <v>1800000</v>
+      </c>
+      <c r="E60" s="20">
+        <v>6300000</v>
+      </c>
+      <c r="F60" s="20">
+        <v>9237822</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" s="20">
+        <v>-500000</v>
+      </c>
+      <c r="C61" s="20">
+        <v>-323100</v>
+      </c>
+      <c r="D61" s="20">
+        <v>200000</v>
+      </c>
+      <c r="E61" s="20">
+        <v>700000</v>
+      </c>
+      <c r="F61" s="20">
+        <v>4557178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="24">
+        <f>IRR(B60:F60)</f>
+        <v>0.3274018030839144</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="11">
+        <f>IRR(B61:F61)</f>
+        <v>0.7478483058961267</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="10">
+        <f>SUM(B61:F61)</f>
+        <v>4634078</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+    </row>
+    <row r="66" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="38">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -1861,7 +1983,10 @@
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="C57:F57"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="A66:F66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1881,7 +2006,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1891,7 +2016,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1911,13 +2036,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1925,13 +2050,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1939,13 +2064,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -1953,13 +2078,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -1967,13 +2092,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="25">
+        <v>106</v>
+      </c>
+      <c r="B9" s="26">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1981,13 +2106,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -1995,13 +2120,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2009,13 +2134,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2023,13 +2148,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2037,13 +2162,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2051,7 +2176,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
@@ -2065,7 +2190,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2073,13 +2198,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2087,7 +2212,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2095,7 +2220,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2103,7 +2228,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -2111,7 +2236,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2121,14 +2246,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B23" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -2136,14 +2261,14 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B24" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -2151,14 +2276,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B25" s="10">
         <f>B24*B9</f>
         <v>9052000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2166,14 +2291,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B26" s="14">
         <f>B25*B10</f>
         <v>2806120</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2181,7 +2306,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2191,14 +2316,14 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B29" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -2206,14 +2331,14 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B30" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -2221,14 +2346,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B31" s="14">
         <f>B30*B14</f>
         <v>1008000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2236,7 +2361,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2246,14 +2371,14 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B34" s="16">
         <f>B23+B29+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -2261,14 +2386,14 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B35" s="16">
         <f>B26+B31</f>
         <v>3814120</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -2276,14 +2401,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B36" s="11">
         <f>B35/B34</f>
         <v>0.0811</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2291,14 +2416,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B37" s="10">
         <f>B34*B18</f>
         <v>28200000</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2306,14 +2431,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B38" s="10">
         <f>B34-B37</f>
         <v>18800000</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2321,14 +2446,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B39" s="11">
         <f>(B35-B37*B19)/B38</f>
         <v>0.098</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2336,7 +2461,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2346,14 +2471,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B42" s="10">
         <f>B35*(1+B20)^4</f>
         <v>4292800</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2361,14 +2486,14 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B43" s="10">
         <f>B42/B17</f>
         <v>53660000</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2376,14 +2501,14 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B44" s="10">
         <f>B43-B37</f>
         <v>25460000</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
@@ -2391,7 +2516,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2401,78 +2526,78 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="26">
+        <v>161</v>
+      </c>
+      <c r="B47" s="27">
         <v>-9400000</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="26">
+        <v>162</v>
+      </c>
+      <c r="B48" s="27">
         <v>-9400000</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B49" s="26">
+        <v>163</v>
+      </c>
+      <c r="B49" s="27">
         <v>900000</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="26">
+        <v>164</v>
+      </c>
+      <c r="B50" s="27">
         <v>1840000</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51" s="26">
+        <v>165</v>
+      </c>
+      <c r="B51" s="27">
         <v>1900000</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B52" s="26">
+        <v>166</v>
+      </c>
+      <c r="B52" s="27">
         <v>1950000</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" s="26">
+        <v>167</v>
+      </c>
+      <c r="B53" s="27">
         <v>2010000</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="26">
+        <v>168</v>
+      </c>
+      <c r="B54" s="27">
         <v>27530000</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B49:B54)/-(B47+B48)</f>
         <v>1.9218085106382978</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -2480,14 +2605,14 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B56" s="27">
+        <v>171</v>
+      </c>
+      <c r="B56" s="24">
         <f>IRR(B47:B54)</f>
         <v>0.12022015409362574</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
@@ -2495,7 +2620,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2505,13 +2630,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B59" s="11">
         <v>0.22</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -2519,14 +2644,14 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B60" s="14">
         <f>B35*(1+B59)</f>
         <v>4653226</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -2534,13 +2659,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B61" s="11">
         <v>0.075</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
@@ -2548,13 +2673,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B62" s="11">
         <v>0.65</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -2562,14 +2687,14 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B63" s="11">
         <f>B60/B34</f>
         <v>0.099</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -2577,14 +2702,14 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B64" s="10">
         <f>B60/B61</f>
         <v>62043015</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -2592,14 +2717,14 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B65" s="10">
         <f>B34*B62</f>
         <v>30550000</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -2607,14 +2732,14 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B66" s="10">
         <f>B34-B65</f>
         <v>16450000</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -2622,14 +2747,14 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B67" s="10">
         <f>B64-B65</f>
         <v>31493015</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -2637,7 +2762,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2647,54 +2772,54 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B70" s="26">
+        <v>161</v>
+      </c>
+      <c r="B70" s="27">
         <v>-8225000</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B71" s="26">
+        <v>162</v>
+      </c>
+      <c r="B71" s="27">
         <v>-8225000</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="26">
+        <v>163</v>
+      </c>
+      <c r="B72" s="27">
         <v>1000000</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" s="26">
+        <v>164</v>
+      </c>
+      <c r="B73" s="27">
         <v>2514726</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B74" s="26">
+        <v>165</v>
+      </c>
+      <c r="B74" s="27">
         <v>34007741</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B75" s="17">
         <f>SUM(B72:B74)/-(B70+B71)</f>
         <v>2.2810010334346504</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
@@ -2702,14 +2827,14 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B76" s="27">
+        <v>193</v>
+      </c>
+      <c r="B76" s="24">
         <f>IRR(B70:B74)</f>
         <v>0.2755427433529377</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
@@ -2717,7 +2842,7 @@
     </row>
     <row r="78" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B78" s="28"/>
       <c r="C78" s="28"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="202">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Development loan (% of total cost)</t>
   </si>
   <si>
-    <t>land-development / A&amp;D financing (70% LTC)</t>
+    <t>land-development / A&amp;D financing (60% LTC)</t>
   </si>
   <si>
     <t>Preferred return</t>
@@ -269,7 +269,7 @@
     <t>Project equity IRR (levered)</t>
   </si>
   <si>
-    <t>equity ~$8.25M (70% LTC); lot sales Yr 2–4. Unlevered project IRR ~24%.</t>
+    <t>equity ~$11M (60% LTC); lot sales Yr 2–4. Unlevered project IRR ~24%.</t>
   </si>
   <si>
     <t>PROMOTE WATERFALL  (LP 90% / GP 10% · 8% pref · 80/20 to 15% · 70/30 to 20% · 60/40 above)</t>
@@ -297,6 +297,24 @@
   </si>
   <si>
     <t>JAL's share of the upside</t>
+  </si>
+  <si>
+    <t>LP IRR SENSITIVITY  (finished lot price  ×  LTC)</t>
+  </si>
+  <si>
+    <t>Lot price  /  LTC</t>
+  </si>
+  <si>
+    <t>$130K / lot</t>
+  </si>
+  <si>
+    <t>$150K / lot</t>
+  </si>
+  <si>
+    <t>$170K / lot</t>
+  </si>
+  <si>
+    <t>LP IRR after the 8% pref + tiered promote. Base case = $150K lot / 60% LTC (highlighted). Each cell re-runs the full waterfall.</t>
   </si>
   <si>
     <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation in further conversations. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
@@ -612,7 +630,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -690,6 +708,16 @@
       <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF6B5A6B"/>
       <sz val="8.5"/>
@@ -741,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -803,16 +831,26 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1154,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1366,7 +1404,7 @@
         <v>27</v>
       </c>
       <c r="B17" s="11">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>28</v>
@@ -1812,19 +1850,19 @@
         <v>83</v>
       </c>
       <c r="B56" s="20">
-        <v>-5000000</v>
+        <v>-6661000</v>
       </c>
       <c r="C56" s="20">
-        <v>-3231000</v>
+        <v>-4313000</v>
       </c>
       <c r="D56" s="20">
-        <v>2000000</v>
+        <v>2247000</v>
       </c>
       <c r="E56" s="20">
-        <v>7000000</v>
+        <v>7840000</v>
       </c>
       <c r="F56" s="20">
-        <v>13795000</v>
+        <v>15451000</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1833,7 +1871,7 @@
       </c>
       <c r="B57" s="22">
         <f>IRR(B56:F56)</f>
-        <v>0.39078273593623514</v>
+        <v>0.3138548910601976</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>85</v>
@@ -1857,19 +1895,19 @@
         <v>87</v>
       </c>
       <c r="B60" s="20">
-        <v>-4500000</v>
+        <v>-5994900</v>
       </c>
       <c r="C60" s="20">
-        <v>-2907900</v>
+        <v>-3881700</v>
       </c>
       <c r="D60" s="20">
-        <v>1800000</v>
+        <v>2022300</v>
       </c>
       <c r="E60" s="20">
-        <v>6300000</v>
+        <v>7056000</v>
       </c>
       <c r="F60" s="20">
-        <v>9237822</v>
+        <v>11235967</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1877,19 +1915,19 @@
         <v>88</v>
       </c>
       <c r="B61" s="20">
-        <v>-500000</v>
+        <v>-666100</v>
       </c>
       <c r="C61" s="20">
-        <v>-323100</v>
+        <v>-431300</v>
       </c>
       <c r="D61" s="20">
-        <v>200000</v>
+        <v>224700</v>
       </c>
       <c r="E61" s="20">
-        <v>700000</v>
+        <v>784000</v>
       </c>
       <c r="F61" s="20">
-        <v>4557178</v>
+        <v>4215033</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1898,7 +1936,7 @@
       </c>
       <c r="B62" s="24">
         <f>IRR(B60:F60)</f>
-        <v>0.3274018030839144</v>
+        <v>0.26842143062633383</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>90</v>
@@ -1913,7 +1951,7 @@
       </c>
       <c r="B63" s="11">
         <f>IRR(B61:F61)</f>
-        <v>0.7478483058961267</v>
+        <v>0.593093661898916</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>92</v>
@@ -1928,7 +1966,7 @@
       </c>
       <c r="B64" s="10">
         <f>SUM(B61:F61)</f>
-        <v>4634078</v>
+        <v>4126333</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>94</v>
@@ -1937,18 +1975,106 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="66" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="25" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="26">
+        <v>0.55</v>
+      </c>
+      <c r="C67" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="D67" s="26">
+        <v>0.65</v>
+      </c>
+      <c r="E67" s="26">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="27">
+        <v>0.18078353298753924</v>
+      </c>
+      <c r="C68" s="27">
+        <v>0.19735068232227648</v>
+      </c>
+      <c r="D68" s="27">
+        <v>0.21556470054605692</v>
+      </c>
+      <c r="E68" s="27">
+        <v>0.23872937985286258</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="27">
+        <v>0.24776127543856818</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0.26841642110322594</v>
+      </c>
+      <c r="D69" s="27">
+        <v>0.2942311832200314</v>
+      </c>
+      <c r="E69" s="27">
+        <v>0.3275162111848672</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="27">
+        <v>0.3066500722851123</v>
+      </c>
+      <c r="C70" s="27">
+        <v>0.33287240798168527</v>
+      </c>
+      <c r="D70" s="27">
+        <v>0.36543747436242235</v>
+      </c>
+      <c r="E70" s="27">
+        <v>0.4065234048048615</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+    </row>
+    <row r="73" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -1986,7 +2112,8 @@
     <mergeCell ref="C62:F62"/>
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="C64:F64"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A73:F73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2006,7 +2133,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2016,7 +2143,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2036,13 +2163,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2050,13 +2177,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2064,13 +2191,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2078,13 +2205,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2092,13 +2219,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="26">
+        <v>112</v>
+      </c>
+      <c r="B9" s="30">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2106,13 +2233,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2120,13 +2247,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2134,13 +2261,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2148,13 +2275,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2162,13 +2289,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2176,7 +2303,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
@@ -2190,7 +2317,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2198,13 +2325,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2212,7 +2339,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2220,7 +2347,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2228,7 +2355,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -2236,7 +2363,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2246,14 +2373,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B23" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -2261,14 +2388,14 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B24" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -2276,14 +2403,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B25" s="10">
         <f>B24*B9</f>
         <v>9052000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2291,14 +2418,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B26" s="14">
         <f>B25*B10</f>
         <v>2806120</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2306,7 +2433,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2316,14 +2443,14 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B29" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -2331,14 +2458,14 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B30" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -2346,14 +2473,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B31" s="14">
         <f>B30*B14</f>
         <v>1008000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2361,7 +2488,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2371,14 +2498,14 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B34" s="16">
         <f>B23+B29+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -2386,14 +2513,14 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B35" s="16">
         <f>B26+B31</f>
         <v>3814120</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -2401,14 +2528,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B36" s="11">
         <f>B35/B34</f>
         <v>0.0811</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2416,14 +2543,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B37" s="10">
         <f>B34*B18</f>
         <v>28200000</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2431,14 +2558,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B38" s="10">
         <f>B34-B37</f>
         <v>18800000</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2446,14 +2573,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B39" s="11">
         <f>(B35-B37*B19)/B38</f>
         <v>0.098</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2461,7 +2588,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2471,14 +2598,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B42" s="10">
         <f>B35*(1+B20)^4</f>
         <v>4292800</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2486,14 +2613,14 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B43" s="10">
         <f>B42/B17</f>
         <v>53660000</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2501,14 +2628,14 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B44" s="10">
         <f>B43-B37</f>
         <v>25460000</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
@@ -2516,7 +2643,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2526,78 +2653,78 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B47" s="27">
+        <v>167</v>
+      </c>
+      <c r="B47" s="31">
         <v>-9400000</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="27">
+        <v>168</v>
+      </c>
+      <c r="B48" s="31">
         <v>-9400000</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" s="27">
+        <v>169</v>
+      </c>
+      <c r="B49" s="31">
         <v>900000</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B50" s="27">
+        <v>170</v>
+      </c>
+      <c r="B50" s="31">
         <v>1840000</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B51" s="27">
+        <v>171</v>
+      </c>
+      <c r="B51" s="31">
         <v>1900000</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B52" s="27">
+        <v>172</v>
+      </c>
+      <c r="B52" s="31">
         <v>1950000</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B53" s="27">
+        <v>173</v>
+      </c>
+      <c r="B53" s="31">
         <v>2010000</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" s="27">
+        <v>174</v>
+      </c>
+      <c r="B54" s="31">
         <v>27530000</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B49:B54)/-(B47+B48)</f>
         <v>1.9218085106382978</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -2605,14 +2732,14 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B56" s="24">
         <f>IRR(B47:B54)</f>
         <v>0.12022015409362574</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
@@ -2620,7 +2747,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2630,13 +2757,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B59" s="11">
         <v>0.22</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -2644,14 +2771,14 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B60" s="14">
         <f>B35*(1+B59)</f>
         <v>4653226</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -2659,13 +2786,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B61" s="11">
         <v>0.075</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
@@ -2673,13 +2800,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B62" s="11">
         <v>0.65</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -2687,14 +2814,14 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B63" s="11">
         <f>B60/B34</f>
         <v>0.099</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -2702,14 +2829,14 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B64" s="10">
         <f>B60/B61</f>
         <v>62043015</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -2717,14 +2844,14 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B65" s="10">
         <f>B34*B62</f>
         <v>30550000</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -2732,14 +2859,14 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B66" s="10">
         <f>B34-B65</f>
         <v>16450000</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -2747,14 +2874,14 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B67" s="10">
         <f>B64-B65</f>
         <v>31493015</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -2762,7 +2889,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2772,54 +2899,54 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B70" s="27">
+        <v>167</v>
+      </c>
+      <c r="B70" s="31">
         <v>-8225000</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" s="27">
+        <v>168</v>
+      </c>
+      <c r="B71" s="31">
         <v>-8225000</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B72" s="27">
+        <v>169</v>
+      </c>
+      <c r="B72" s="31">
         <v>1000000</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B73" s="27">
+        <v>170</v>
+      </c>
+      <c r="B73" s="31">
         <v>2514726</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B74" s="27">
+        <v>171</v>
+      </c>
+      <c r="B74" s="31">
         <v>34007741</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B75" s="17">
         <f>SUM(B72:B74)/-(B70+B71)</f>
         <v>2.2810010334346504</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
@@ -2827,28 +2954,28 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B76" s="24">
         <f>IRR(B70:B74)</f>
         <v>0.2755427433529377</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
     <row r="78" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
+      <c r="A78" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="43">

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="208">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
@@ -290,13 +290,13 @@
     <t>GP IRR (co-invest + carried interest)</t>
   </si>
   <si>
-    <t>JAL</t>
+    <t>sponsor group — Capital H6 / Bob / JAL + partners</t>
   </si>
   <si>
     <t>GP net profit (co-invest + promote)</t>
   </si>
   <si>
-    <t>JAL's share of the upside</t>
+    <t>GP group total — JAL earns a share</t>
   </si>
   <si>
     <t>LP IRR SENSITIVITY  (finished lot price  ×  LTC)</t>
@@ -615,6 +615,24 @@
   </si>
   <si>
     <t>recap / sell at stabilization</t>
+  </si>
+  <si>
+    <t>BUILD-TO-CORE IRR SENSITIVITY  (stabilized NOI  ×  exit cap)</t>
+  </si>
+  <si>
+    <t>Stabilized NOI  /  exit cap</t>
+  </si>
+  <si>
+    <t>$4.2M NOI</t>
+  </si>
+  <si>
+    <t>$4.65M NOI (base)</t>
+  </si>
+  <si>
+    <t>$5.15M NOI</t>
+  </si>
+  <si>
+    <t>Build-to-core project IRR at 65% LTC, recap at stabilization (~Yr 4). Base = $4.65M NOI / 7.5% cap (highlighted). Each cell re-runs the model.</t>
   </si>
   <si>
     <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold). VIVAMEE operates; JAL is the capital partner (debt + equity placement fees, co-invest, promote). The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
@@ -769,7 +787,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -849,6 +867,9 @@
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2122,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2967,18 +2988,106 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="78" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="32" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79" s="32">
+        <v>0.07</v>
+      </c>
+      <c r="C79" s="32">
+        <v>0.075</v>
+      </c>
+      <c r="D79" s="32">
+        <v>0.08</v>
+      </c>
+      <c r="E79" s="32">
+        <v>0.085</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80" s="27">
+        <v>0.2413590494653527</v>
+      </c>
+      <c r="C80" s="27">
+        <v>0.1981010805160578</v>
+      </c>
+      <c r="D80" s="27">
+        <v>0.15643182900562425</v>
+      </c>
+      <c r="E80" s="27">
+        <v>0.11594756701498155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B81" s="27">
+        <v>0.3166711576166231</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0.27563551751308235</v>
+      </c>
+      <c r="D81" s="27">
+        <v>0.2365089547947662</v>
+      </c>
+      <c r="E81" s="27">
+        <v>0.1989302587607228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" s="27">
+        <v>0.3879656267349022</v>
+      </c>
+      <c r="C82" s="27">
+        <v>0.3484741336946878</v>
+      </c>
+      <c r="D82" s="27">
+        <v>0.31109801406577653</v>
+      </c>
+      <c r="E82" s="27">
+        <v>0.2754915069098355</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="85" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85" s="33"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="33"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -3021,7 +3130,8 @@
     <mergeCell ref="C67:F67"/>
     <mergeCell ref="C75:F75"/>
     <mergeCell ref="C76:F76"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -7,17 +7,17 @@
     <sheet sheetId="1" name="Finished-Lot Model" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Phase 2 — Hospitality" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="229">
   <si>
     <t>Queenstown Harbor — Finished-Lot Development Model</t>
   </si>
   <si>
-    <t>JV funds the horizontal (roads, sewer, utilities); homebuilders just build the homes.  ·  ILLUSTRATIVE — subject to survey, easement, entitlement &amp; capital terms.</t>
+    <t>JV funds the horizontal (roads, sewer, utilities); homebuilders just build the homes.  ·  Dynamic — every cell below is a live formula off INPUTS.  ·  ILLUSTRATIVE.</t>
   </si>
   <si>
     <t>INPUTS  (edit these — everything below recalculates)</t>
@@ -185,13 +185,13 @@
     <t>land-development financing</t>
   </si>
   <si>
-    <t>Land equity (H6)</t>
+    <t>Land equity (contributed)</t>
   </si>
   <si>
     <t>contributed land</t>
   </si>
   <si>
-    <t>Cash equity (JAL + LP)</t>
+    <t>Cash equity</t>
   </si>
   <si>
     <t>balance — co-invest + LP raise</t>
@@ -224,16 +224,22 @@
     <t>land contribution + cash equity</t>
   </si>
   <si>
+    <t>Distributable to equity (capital + profit)</t>
+  </si>
+  <si>
+    <t>returned to equity over the hold</t>
+  </si>
+  <si>
     <t>Equity multiple</t>
   </si>
   <si>
-    <t>(equity + profit) / equity, levered</t>
-  </si>
-  <si>
-    <t>PHASED PROJECT CASH FLOW  (unlevered, $ — for IRR)</t>
-  </si>
-  <si>
-    <t>Year</t>
+    <t>distributable / equity, levered</t>
+  </si>
+  <si>
+    <t>CASH-FLOW TIMING  (% by year — edit to re-phase; each row sums to 100%)</t>
+  </si>
+  <si>
+    <t>$ by year</t>
   </si>
   <si>
     <t>Yr 0</t>
@@ -251,16 +257,43 @@
     <t>Yr 4</t>
   </si>
   <si>
+    <t>Revenue phasing (lot sales)</t>
+  </si>
+  <si>
+    <t>Cost phasing (land/horizontal/soft)</t>
+  </si>
+  <si>
+    <t>Equity-draw phasing</t>
+  </si>
+  <si>
+    <t>Equity-distribution phasing</t>
+  </si>
+  <si>
+    <t>UNLEVERED PROJECT CASH FLOW  (revenue × phasing − cost × phasing)</t>
+  </si>
+  <si>
+    <t>Lot revenue</t>
+  </si>
+  <si>
+    <t>Total cost</t>
+  </si>
+  <si>
     <t>Net project cash flow</t>
   </si>
   <si>
     <t>Project IRR (unlevered)</t>
   </si>
   <si>
-    <t>entitlement/land Yr 0–1, horizontal Yr 1–2, finished-lot sales Yr 2–4</t>
-  </si>
-  <si>
-    <t>LEVERED EQUITY RETURN  (70% LTC development loan)</t>
+    <t>lots sell Yr 2–4; land &amp; horizontal up front</t>
+  </si>
+  <si>
+    <t>LEVERED EQUITY CASH FLOW  (60% LTC development loan)</t>
+  </si>
+  <si>
+    <t>Equity drawn</t>
+  </si>
+  <si>
+    <t>Equity distributions</t>
   </si>
   <si>
     <t>Project equity cash flow</t>
@@ -269,7 +302,7 @@
     <t>Project equity IRR (levered)</t>
   </si>
   <si>
-    <t>equity ~$11M (60% LTC); lot sales Yr 2–4. Unlevered project IRR ~24%.</t>
+    <t>equity ~$11.0M; unlevered project IRR ~24%</t>
   </si>
   <si>
     <t>PROMOTE WATERFALL  (LP 90% / GP 10% · 8% pref · 80/20 to 15% · 70/30 to 20% · 60/40 above)</t>
@@ -299,6 +332,9 @@
     <t>GP group total — JAL earns a share</t>
   </si>
   <si>
+    <t>LP / GP split is solved by the model's promote engine (an IRR-hurdle waterfall isn't a closed-form cell formula); the IRR / profit cells above are live over those rows.</t>
+  </si>
+  <si>
     <t>LP IRR SENSITIVITY  (finished lot price  ×  LTC)</t>
   </si>
   <si>
@@ -314,16 +350,16 @@
     <t>$170K / lot</t>
   </si>
   <si>
-    <t>LP IRR after the 8% pref + tiered promote. Base case = $150K lot / 60% LTC (highlighted). Each cell re-runs the full waterfall.</t>
-  </si>
-  <si>
-    <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation in further conversations. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
+    <t>LP IRR after the 8% pref + tiered promote. Base = $150K lot / 60% LTC (highlighted). Each cell re-runs the full waterfall engine.</t>
+  </si>
+  <si>
+    <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
   </si>
   <si>
     <t>Queenstown Harbor — Phase 2: Hospitality (Hotel + Restaurants)</t>
   </si>
   <si>
-    <t>VIVAMEE-led resort; JAL as capital partner. Income / hold play — develops to ~cost; returns come from cash flow + appreciation.  ·  ILLUSTRATIVE.</t>
+    <t>VIVÂMEE-led resort; JAL leads capital formation.  ·  Dynamic — every cell below is a live formula off INPUTS.  ·  ILLUSTRATIVE.</t>
   </si>
   <si>
     <t>Hotel — keys</t>
@@ -392,7 +428,7 @@
     <t>Soft / FF&amp;E / pre-opening ($)</t>
   </si>
   <si>
-    <t>Exit cap rate</t>
+    <t>Exit cap rate (hold case)</t>
   </si>
   <si>
     <t>hotel cap ~8% (2025)</t>
@@ -407,31 +443,43 @@
     <t>NOI growth / yr</t>
   </si>
   <si>
+    <t>Equity drawn — Year 0 (balance Yr 1)</t>
+  </si>
+  <si>
+    <t>construction equity timing</t>
+  </si>
+  <si>
+    <t>First operating year ramp (hold)</t>
+  </si>
+  <si>
+    <t>Yr 2 opens partway through</t>
+  </si>
+  <si>
     <t>HOTEL</t>
   </si>
   <si>
     <t>Hotel development cost</t>
   </si>
   <si>
-    <t>keys x cost/key</t>
+    <t>keys × cost/key</t>
   </si>
   <si>
     <t>Room revenue</t>
   </si>
   <si>
-    <t>keys x 365 x ADR x occ</t>
+    <t>keys × 365 × ADR × occ</t>
   </si>
   <si>
     <t>Total hotel revenue</t>
   </si>
   <si>
-    <t>x revenue multiple</t>
+    <t>× revenue multiple</t>
   </si>
   <si>
     <t>Hotel NOI (stabilized)</t>
   </si>
   <si>
-    <t>x NOI margin</t>
+    <t>× NOI margin</t>
   </si>
   <si>
     <t>RESTAURANTS  (a suite of nice restaurants)</t>
@@ -440,13 +488,13 @@
     <t>Restaurant development cost</t>
   </si>
   <si>
-    <t>SF x cost/SF</t>
+    <t>SF × cost/SF</t>
   </si>
   <si>
     <t>Restaurant sales</t>
   </si>
   <si>
-    <t>SF x sales/SF</t>
+    <t>SF × sales/SF</t>
   </si>
   <si>
     <t>Restaurant NOI (to owner)</t>
@@ -482,88 +530,94 @@
     <t>Equity (land + cash)</t>
   </si>
   <si>
-    <t>cost - loan</t>
+    <t>cost − loan</t>
+  </si>
+  <si>
+    <t>Stabilized levered cash flow</t>
+  </si>
+  <si>
+    <t>NOI − loan interest</t>
   </si>
   <si>
     <t>Cash-on-cash (stabilized, levered)</t>
   </si>
   <si>
-    <t>(NOI - interest) / equity</t>
-  </si>
-  <si>
-    <t>EXIT  &amp;  RETURNS  (7-year hold)</t>
-  </si>
-  <si>
-    <t>Year-7 NOI (3%/yr growth)</t>
-  </si>
-  <si>
-    <t>stabilized x growth</t>
+    <t>stabilized levered CF / equity</t>
+  </si>
+  <si>
+    <t>EXIT  (hold case — sell at exit cap)</t>
+  </si>
+  <si>
+    <t>Exit-year NOI (+3%/yr × 4)</t>
+  </si>
+  <si>
+    <t>stabilized × growth</t>
   </si>
   <si>
     <t>Exit value (@ exit cap)</t>
   </si>
   <si>
-    <t>Year-7 NOI / cap</t>
-  </si>
-  <si>
-    <t>Exit equity (value - loan)</t>
+    <t>exit-year NOI / cap</t>
+  </si>
+  <si>
+    <t>Exit equity (value − loan)</t>
   </si>
   <si>
     <t>net of loan</t>
   </si>
   <si>
-    <t>EQUITY CASH FLOW (levered, $) &amp; RETURNS</t>
-  </si>
-  <si>
-    <t>Year 0</t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <t>Year 5</t>
-  </si>
-  <si>
-    <t>Year 6</t>
-  </si>
-  <si>
-    <t>Year 7</t>
-  </si>
-  <si>
-    <t>Equity multiple (7-yr)</t>
+    <t>HOLD-CASE EQUITY CASH FLOW  (Yr 0–7, levered $) &amp; RETURNS</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 0</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 1</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 2</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 3</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 4</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 5</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 6</t>
+  </si>
+  <si>
+    <t>Equity CF — Year 7</t>
+  </si>
+  <si>
+    <t>Equity multiple (7-yr hold)</t>
   </si>
   <si>
     <t>distributions / equity</t>
   </si>
   <si>
-    <t>Project IRR (levered, 7-yr)</t>
-  </si>
-  <si>
-    <t>equity cash flows Yr 0–7</t>
-  </si>
-  <si>
-    <t>BUILD-TO-CORE CASE  (path to mid–high 20s IRR — recap / sell at stabilization)</t>
+    <t>Project IRR (levered, 7-yr hold)</t>
+  </si>
+  <si>
+    <t>income / hold — develops to ~cost</t>
+  </si>
+  <si>
+    <t>BUILD-TO-CORE CASE  (recap / sell at stabilization — path to mid–high 20s IRR)</t>
   </si>
   <si>
     <t>NOI uplift — premium execution</t>
   </si>
   <si>
-    <t>VIVAMEE experiential: ADR ~$275, occ ~63%, strong F&amp;B / events</t>
+    <t>VIVÂMEE experiential: ADR ~$275, occ ~63%, strong F&amp;B / events</t>
   </si>
   <si>
     <t>Premium stabilized NOI</t>
   </si>
   <si>
-    <t>base NOI x (1 + uplift)</t>
+    <t>base NOI × (1 + uplift)</t>
   </si>
   <si>
     <t>Exit cap (build-to-core)</t>
@@ -578,6 +632,9 @@
     <t>construction loan</t>
   </si>
   <si>
+    <t>First operating year ramp (b-t-c)</t>
+  </si>
+  <si>
     <t>Yield on cost (premium)</t>
   </si>
   <si>
@@ -599,10 +656,16 @@
     <t>Equity</t>
   </si>
   <si>
+    <t>Premium stabilized levered cash flow</t>
+  </si>
+  <si>
+    <t>premium NOI − loan interest</t>
+  </si>
+  <si>
     <t>at recap / sale</t>
   </si>
   <si>
-    <t>BUILD-TO-CORE EQUITY CASH FLOW (Yr 0–4, $) &amp; RETURNS</t>
+    <t>BUILD-TO-CORE EQUITY CASH FLOW  (Yr 0–4, levered $) &amp; RETURNS</t>
   </si>
   <si>
     <t>Equity multiple (build-to-core)</t>
@@ -632,10 +695,10 @@
     <t>$5.15M NOI</t>
   </si>
   <si>
-    <t>Build-to-core project IRR at 65% LTC, recap at stabilization (~Yr 4). Base = $4.65M NOI / 7.5% cap (highlighted). Each cell re-runs the model.</t>
-  </si>
-  <si>
-    <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold). VIVAMEE operates; JAL is the capital partner (debt + equity placement fees, co-invest, promote). The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
+    <t>Build-to-core project IRR at 65% LTC, recap at stabilization (~Yr 4). Base = $4.65M NOI / 7.5% cap (highlighted). Each cell re-runs the engine.</t>
+  </si>
+  <si>
+    <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold) — unless you build to core and recap at stabilization. VIVÂMEE operates; JAL leads capital formation. The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
   </si>
 </sst>
 </file>
@@ -648,7 +711,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -701,29 +764,12 @@
       <b/>
       <color rgb="FF6B5A6B"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="FF333333"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF0B163C"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0B163C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF3A243A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF6B5A6B"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -736,14 +782,18 @@
       <sz val="10"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF6B5A6B"/>
-      <sz val="8.5"/>
+      <b/>
+      <color rgb="FF0B163C"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="FF0B163C"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF3A243A"/>
+      <sz val="10"/>
     </font>
     <font>
       <i/>
@@ -787,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -831,48 +881,41 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1213,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1729,7 +1772,7 @@
       </c>
       <c r="B44" s="11">
         <f>B43/B25</f>
-        <v>0.35</v>
+        <v>0.34676190476190477</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1738,7 +1781,7 @@
       </c>
       <c r="B45" s="11">
         <f>B43/B34</f>
-        <v>0.537</v>
+        <v>0.5308353987461729</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1757,12 +1800,12 @@
       <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="17">
-        <f>(B46+B43)/B46</f>
-        <v>2.34</v>
+      <c r="B47" s="10">
+        <f>B46+B43</f>
+        <v>25538400</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>71</v>
@@ -1771,193 +1814,243 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="B48" s="17">
+        <f>B47/B46</f>
+        <v>2.327088496865432</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>73</v>
-      </c>
-      <c r="B50" s="18" t="s">
+      <c r="A50" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="B51" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="C51" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F50" s="18" t="s">
+      <c r="D51" s="19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="E51" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="20">
-        <v>-8000000</v>
-      </c>
-      <c r="C51" s="20">
-        <v>-10000000</v>
-      </c>
-      <c r="D51" s="20">
-        <v>2500000</v>
-      </c>
-      <c r="E51" s="20">
-        <v>18000000</v>
-      </c>
-      <c r="F51" s="20">
-        <v>12000000</v>
+      <c r="F51" s="19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="20">
+        <v>0</v>
+      </c>
+      <c r="C52" s="20">
+        <v>0</v>
+      </c>
+      <c r="D52" s="20">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="E52" s="20">
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="F52" s="20">
+        <v>0.40476190476190477</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="20">
+        <v>0.22</v>
+      </c>
+      <c r="C53" s="20">
+        <v>0.38</v>
+      </c>
+      <c r="D53" s="20">
+        <v>0.36</v>
+      </c>
+      <c r="E53" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="F53" s="20">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="20">
+        <v>0.607</v>
+      </c>
+      <c r="C54" s="20">
+        <v>0.393</v>
+      </c>
+      <c r="D54" s="20">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20">
+        <v>0</v>
+      </c>
+      <c r="F54" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="20">
+        <v>0</v>
+      </c>
+      <c r="C55" s="20">
+        <v>0</v>
+      </c>
+      <c r="D55" s="20">
+        <v>0.088</v>
+      </c>
+      <c r="E55" s="20">
+        <v>0.307</v>
+      </c>
+      <c r="F55" s="20">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B52" s="22">
-        <f>IRR(B51:F51)</f>
-        <v>0.24221266248453055</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="20">
-        <v>-6661000</v>
-      </c>
-      <c r="C56" s="20">
-        <v>-4313000</v>
-      </c>
-      <c r="D56" s="20">
-        <v>2247000</v>
-      </c>
-      <c r="E56" s="20">
-        <v>7840000</v>
-      </c>
-      <c r="F56" s="20">
-        <v>15451000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="22">
-        <f>IRR(B56:F56)</f>
-        <v>0.3138548910601976</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="B59" s="21">
+        <f>$B$25*B52</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="21">
+        <f>$B$25*C52</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="21">
+        <f>$B$25*D52</f>
+        <v>8000000</v>
+      </c>
+      <c r="E59" s="21">
+        <f>$B$25*E52</f>
+        <v>17000000</v>
+      </c>
+      <c r="F59" s="21">
+        <f>$B$25*F52</f>
+        <v>17000000</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
+      <c r="A60" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="20">
-        <v>-5994900</v>
-      </c>
-      <c r="C60" s="20">
-        <v>-3881700</v>
-      </c>
-      <c r="D60" s="20">
-        <v>2022300</v>
-      </c>
-      <c r="E60" s="20">
-        <v>7056000</v>
-      </c>
-      <c r="F60" s="20">
-        <v>11235967</v>
+      <c r="B60" s="21">
+        <f>-$B$34*B53</f>
+        <v>-6035920</v>
+      </c>
+      <c r="C60" s="21">
+        <f>-$B$34*C53</f>
+        <v>-10425680</v>
+      </c>
+      <c r="D60" s="21">
+        <f>-$B$34*D53</f>
+        <v>-9876960</v>
+      </c>
+      <c r="E60" s="21">
+        <f>-$B$34*E53</f>
+        <v>-823080</v>
+      </c>
+      <c r="F60" s="21">
+        <f>-$B$34*F53</f>
+        <v>-274360</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
+      <c r="A61" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="20">
-        <v>-666100</v>
-      </c>
-      <c r="C61" s="20">
-        <v>-431300</v>
-      </c>
-      <c r="D61" s="20">
-        <v>224700</v>
-      </c>
-      <c r="E61" s="20">
-        <v>784000</v>
-      </c>
-      <c r="F61" s="20">
-        <v>4215033</v>
+      <c r="B61" s="14">
+        <f>B59+B60</f>
+        <v>-6035920</v>
+      </c>
+      <c r="C61" s="14">
+        <f>C59+C60</f>
+        <v>-10425680</v>
+      </c>
+      <c r="D61" s="14">
+        <f>D59+D60</f>
+        <v>-1876960</v>
+      </c>
+      <c r="E61" s="14">
+        <f>E59+E60</f>
+        <v>16176920</v>
+      </c>
+      <c r="F61" s="14">
+        <f>F59+F60</f>
+        <v>16725640</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="24">
-        <f>IRR(B60:F60)</f>
-        <v>0.26842143062633383</v>
+      <c r="B62" s="22">
+        <f>IRR(B61:F61)</f>
+        <v>0.23697429468401643</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>90</v>
@@ -1966,136 +2059,351 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B63" s="11">
-        <f>IRR(B61:F61)</f>
-        <v>0.593093661898916</v>
-      </c>
-      <c r="C63" s="8" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
+      <c r="B66" s="21">
+        <f>-$B$46*B54</f>
+        <v>-6661460.8</v>
+      </c>
+      <c r="C66" s="21">
+        <f>-$B$46*C54</f>
+        <v>-4312939.2</v>
+      </c>
+      <c r="D66" s="21">
+        <f>-$B$46*D54</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="21">
+        <f>-$B$46*E54</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="21">
+        <f>-$B$46*F54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B64" s="10">
-        <f>SUM(B61:F61)</f>
-        <v>4126333</v>
-      </c>
-      <c r="C64" s="8" t="s">
+      <c r="B67" s="21">
+        <f>$B$47*B55</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="21">
+        <f>$B$47*C55</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="21">
+        <f>$B$47*D55</f>
+        <v>2247379.1999999997</v>
+      </c>
+      <c r="E67" s="21">
+        <f>$B$47*E55</f>
+        <v>7840288.8</v>
+      </c>
+      <c r="F67" s="21">
+        <f>$B$47*F55</f>
+        <v>15450732</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="B68" s="10">
+        <f>B66+B67</f>
+        <v>-6661460.8</v>
+      </c>
+      <c r="C68" s="10">
+        <f>C66+C67</f>
+        <v>-4312939.2</v>
+      </c>
+      <c r="D68" s="10">
+        <f>D66+D67</f>
+        <v>2247379.1999999997</v>
+      </c>
+      <c r="E68" s="10">
+        <f>E66+E67</f>
+        <v>7840288.8</v>
+      </c>
+      <c r="F68" s="10">
+        <f>F66+F67</f>
+        <v>15450732</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="25" t="s">
+      <c r="B69" s="22">
+        <f>IRR(B68:F68)</f>
+        <v>0.31384809341597164</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B67" s="26">
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="21">
+        <v>-5995315</v>
+      </c>
+      <c r="C73" s="21">
+        <v>-3881645</v>
+      </c>
+      <c r="D73" s="21">
+        <v>2022641</v>
+      </c>
+      <c r="E73" s="21">
+        <v>7056260</v>
+      </c>
+      <c r="F73" s="21">
+        <v>11235772</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" s="21">
+        <v>-666146</v>
+      </c>
+      <c r="C74" s="21">
+        <v>-431294</v>
+      </c>
+      <c r="D74" s="21">
+        <v>224738</v>
+      </c>
+      <c r="E74" s="21">
+        <v>784029</v>
+      </c>
+      <c r="F74" s="21">
+        <v>4214960</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="22">
+        <f>IRR(B73:F73)</f>
+        <v>0.26841642110322594</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" s="11">
+        <f>IRR(B74:F74)</f>
+        <v>0.5930774883918588</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B77" s="10">
+        <f>SUM(B74:F74)</f>
+        <v>4126286</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" s="24">
         <v>0.55</v>
       </c>
-      <c r="C67" s="26">
+      <c r="C81" s="24">
         <v>0.6</v>
       </c>
-      <c r="D67" s="26">
+      <c r="D81" s="24">
         <v>0.65</v>
       </c>
-      <c r="E67" s="26">
+      <c r="E81" s="24">
         <v>0.7</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="27">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" s="26">
         <v>0.18078353298753924</v>
       </c>
-      <c r="C68" s="27">
+      <c r="C82" s="26">
         <v>0.19735068232227648</v>
       </c>
-      <c r="D68" s="27">
+      <c r="D82" s="26">
         <v>0.21556470054605692</v>
       </c>
-      <c r="E68" s="27">
+      <c r="E82" s="26">
         <v>0.23872937985286258</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="27">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" s="26">
         <v>0.24776127543856818</v>
       </c>
-      <c r="C69" s="28">
+      <c r="C83" s="27">
         <v>0.26841642110322594</v>
       </c>
-      <c r="D69" s="27">
+      <c r="D83" s="26">
         <v>0.2942311832200314</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E83" s="26">
         <v>0.3275162111848672</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="27">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="26">
         <v>0.3066500722851123</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C84" s="26">
         <v>0.33287240798168527</v>
       </c>
-      <c r="D70" s="27">
+      <c r="D84" s="26">
         <v>0.36543747436242235</v>
       </c>
-      <c r="E70" s="27">
+      <c r="E84" s="26">
         <v>0.4065234048048615</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-    </row>
-    <row r="73" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+    </row>
+    <row r="87" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" s="28"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -2128,13 +2436,15 @@
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2143,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2154,7 +2464,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2164,7 +2474,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2184,13 +2494,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2198,13 +2508,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2212,13 +2522,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2226,13 +2536,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2240,13 +2550,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="30">
+        <v>124</v>
+      </c>
+      <c r="B9" s="29">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2254,13 +2564,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2268,13 +2578,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2282,13 +2592,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2296,13 +2606,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2310,13 +2620,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2324,7 +2634,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
@@ -2338,7 +2648,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2346,13 +2656,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2360,7 +2670,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2368,7 +2678,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2376,217 +2686,215 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
       </c>
     </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="10">
+      <c r="A22" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="10">
-        <f>B5*365*B7*B8</f>
-        <v>5657500</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="10">
-        <f>B24*B9</f>
-        <v>9052000</v>
-      </c>
       <c r="C25" s="8" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B26" s="14">
-        <f>B25*B10</f>
-        <v>2806120</v>
+      <c r="A26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="10">
+        <f>B5*365*B7*B8</f>
+        <v>5657500</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="10">
+        <f>B26*B9</f>
+        <v>9052000</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+    </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29" s="10">
+      <c r="A28" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="14">
+        <f>B27*B10</f>
+        <v>2806120</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="10">
-        <f>B11*B13</f>
-        <v>11200000</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" s="14">
-        <f>B30*B14</f>
-        <v>1008000</v>
-      </c>
       <c r="C31" s="8" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="10">
+        <f>B11*B13</f>
+        <v>11200000</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+    </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="16">
-        <f>B23+B29+B15+B16</f>
+      <c r="A33" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="14">
+        <f>B32*B14</f>
+        <v>1008000</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="16">
+        <f>B25+B31+B15+B16</f>
         <v>47000000</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="16">
-        <f>B26+B31</f>
-        <v>3814120</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36" s="11">
-        <f>B35/B34</f>
-        <v>0.0811</v>
-      </c>
       <c r="C36" s="8" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B37" s="10">
-        <f>B34*B18</f>
-        <v>28200000</v>
+      <c r="A37" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="16">
+        <f>B28+B33</f>
+        <v>3814120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B38" s="10">
-        <f>B34-B37</f>
-        <v>18800000</v>
+      <c r="A38" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="11">
+        <f>B37/B36</f>
+        <v>0.08115148936170213</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2594,240 +2902,250 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B39" s="11">
-        <f>(B35-B37*B19)/B38</f>
-        <v>0.098</v>
+        <v>169</v>
+      </c>
+      <c r="B39" s="10">
+        <f>B36*B18</f>
+        <v>28200000</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="10">
+        <f>B36-B39</f>
+        <v>18800000</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+    </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="10">
+        <f>B37-B39*B19</f>
+        <v>1840119.9999999998</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B42" s="10">
-        <f>B35*(1+B20)^4</f>
-        <v>4292800</v>
+        <v>175</v>
+      </c>
+      <c r="B42" s="11">
+        <f>B41/B40</f>
+        <v>0.09787872340425531</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B43" s="10">
-        <f>B42/B17</f>
-        <v>53660000</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B44" s="10">
-        <f>B43-B37</f>
-        <v>25460000</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="A44" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" s="10">
+        <f>B37*(1+B20)^4</f>
+        <v>4292825.6623972</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="10">
+        <f>B45/B17</f>
+        <v>53660320.779965</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B47" s="31">
-        <v>-9400000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B48" s="31">
-        <v>-9400000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="31">
-        <v>900000</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B47" s="10">
+        <f>B46-B39</f>
+        <v>25460320.779965</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B50" s="31">
-        <v>1840000</v>
+        <v>185</v>
+      </c>
+      <c r="B50" s="21">
+        <f>-B40*B21</f>
+        <v>-9400000</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B51" s="31">
-        <v>1900000</v>
+        <v>186</v>
+      </c>
+      <c r="B51" s="21">
+        <f>-B40*(1-B21)</f>
+        <v>-9400000</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="31">
-        <v>1950000</v>
+        <v>187</v>
+      </c>
+      <c r="B52" s="21">
+        <f>B41*B22</f>
+        <v>920059.9999999999</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B53" s="31">
-        <v>2010000</v>
+        <v>188</v>
+      </c>
+      <c r="B53" s="21">
+        <f>B41</f>
+        <v>1840119.9999999998</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B54" s="31">
-        <v>27530000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B55" s="17">
-        <f>SUM(B49:B54)/-(B47+B48)</f>
-        <v>1.9218085106382978</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B56" s="24">
-        <f>IRR(B47:B54)</f>
-        <v>0.12022015409362574</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+        <v>189</v>
+      </c>
+      <c r="B54" s="21">
+        <f>B41*(1+B20)</f>
+        <v>1895323.5999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="21">
+        <f>B41*(1+B20)^2</f>
+        <v>1952183.3079999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" s="21">
+        <f>B41*(1+B20)^3</f>
+        <v>2010748.8072399998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B57" s="21">
+        <f>B41*(1+B20)^4+B47</f>
+        <v>27531392.051422197</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="A58" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="17">
+        <f>SUM(B52:B57)/-(B50+B51)</f>
+        <v>1.9228631790777764</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B59" s="11">
-        <v>0.22</v>
+      <c r="A59" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B59" s="22">
+        <f>IRR(B50:B57)</f>
+        <v>0.12039129900378642</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B60" s="14">
-        <f>B35*(1+B59)</f>
-        <v>4653226</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-    </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B61" s="11">
-        <v>0.075</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
+      <c r="A61" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B62" s="11">
-        <v>0.65</v>
+        <v>0.22</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -2835,29 +3153,28 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="B63" s="11">
-        <f>B60/B34</f>
-        <v>0.099</v>
+        <v>200</v>
+      </c>
+      <c r="B63" s="14">
+        <f>B37*(1+B62)</f>
+        <v>4653226.399999999</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="10">
-        <f>B60/B61</f>
-        <v>62043015</v>
+      <c r="A64" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" s="11">
+        <v>0.075</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -2865,14 +3182,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B65" s="10">
-        <f>B34*B62</f>
-        <v>30550000</v>
+        <v>204</v>
+      </c>
+      <c r="B65" s="11">
+        <v>0.65</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -2880,214 +3196,293 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B66" s="10">
-        <f>B34-B65</f>
-        <v>16450000</v>
+        <v>206</v>
+      </c>
+      <c r="B66" s="11">
+        <v>0.4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B67" s="10">
-        <f>B64-B65</f>
-        <v>31493015</v>
+      <c r="A67" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="11">
+        <f>B63/B36</f>
+        <v>0.09900481702127659</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B68" s="10">
+        <f>B63/B64</f>
+        <v>62043018.666666664</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+    </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="10">
+        <f>B36*B65</f>
+        <v>30550000</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B70" s="31">
+        <v>213</v>
+      </c>
+      <c r="B70" s="10">
+        <f>B36-B69</f>
+        <v>16450000</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B71" s="10">
+        <f>B63-B69*B19</f>
+        <v>2514726.3999999994</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" s="10">
+        <f>B68-B69</f>
+        <v>31493018.666666664</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="21">
+        <f>-B70*B21</f>
         <v>-8225000</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B71" s="31">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" s="21">
+        <f>-B70*(1-B21)</f>
         <v>-8225000</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B72" s="31">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="31">
-        <v>2514726</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B74" s="31">
-        <v>34007741</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B75" s="17">
-        <f>SUM(B72:B74)/-(B70+B71)</f>
-        <v>2.2810010334346504</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B76" s="24">
-        <f>IRR(B70:B74)</f>
-        <v>0.2755427433529377</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B79" s="32">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B77" s="21">
+        <f>B71*B66</f>
+        <v>1005890.5599999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B78" s="21">
+        <f>B71</f>
+        <v>2514726.3999999994</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B79" s="21">
+        <f>B71+B72</f>
+        <v>34007745.06666666</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B80" s="17">
+        <f>SUM(B77:B79)/-(B75+B76)</f>
+        <v>2.281359393718338</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B81" s="22">
+        <f>IRR(B75:B79)</f>
+        <v>0.27563551751308235</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B84" s="30">
         <v>0.07</v>
       </c>
-      <c r="C79" s="32">
+      <c r="C84" s="30">
         <v>0.075</v>
       </c>
-      <c r="D79" s="32">
+      <c r="D84" s="30">
         <v>0.08</v>
       </c>
-      <c r="E79" s="32">
+      <c r="E84" s="30">
         <v>0.085</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B80" s="27">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B85" s="26">
         <v>0.2413590494653527</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C85" s="26">
         <v>0.1981010805160578</v>
       </c>
-      <c r="D80" s="27">
+      <c r="D85" s="26">
         <v>0.15643182900562425</v>
       </c>
-      <c r="E80" s="27">
+      <c r="E85" s="26">
         <v>0.11594756701498155</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" s="27">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B86" s="26">
         <v>0.3166711576166231</v>
       </c>
-      <c r="C81" s="28">
+      <c r="C86" s="27">
         <v>0.27563551751308235</v>
       </c>
-      <c r="D81" s="27">
+      <c r="D86" s="26">
         <v>0.2365089547947662</v>
       </c>
-      <c r="E81" s="27">
+      <c r="E86" s="26">
         <v>0.1989302587607228</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="B82" s="27">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B87" s="26">
         <v>0.3879656267349022</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C87" s="26">
         <v>0.3484741336946878</v>
       </c>
-      <c r="D82" s="27">
+      <c r="D87" s="26">
         <v>0.31109801406577653</v>
       </c>
-      <c r="E82" s="27">
+      <c r="E87" s="26">
         <v>0.2754915069098355</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-    </row>
-    <row r="85" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="B85" s="33"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="33"/>
-      <c r="E85" s="33"/>
-      <c r="F85" s="33"/>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="90" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="49">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -3101,37 +3496,42 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C58:F58"/>
     <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
     <mergeCell ref="C62:F62"/>
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="C64:F64"/>
     <mergeCell ref="C65:F65"/>
     <mergeCell ref="C66:F66"/>
     <mergeCell ref="C67:F67"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A90:F90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -323,7 +323,7 @@
     <t>GP IRR (co-invest + carried interest)</t>
   </si>
   <si>
-    <t>sponsor group — Capital H6 / Bob / JAL + partners</t>
+    <t>sponsor group — Accountable Equity / Capital H6 / Bob / JAL + partners</t>
   </si>
   <si>
     <t>GP net profit (co-invest + promote)</t>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Finished-Lot Model" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Entitled-Lot Model" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Phase 2 — Hospitality" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="229">
-  <si>
-    <t>Queenstown Harbor — Finished-Lot Development Model</t>
-  </si>
-  <si>
-    <t>JV funds the horizontal (roads, sewer, utilities); homebuilders just build the homes.  ·  Dynamic — every cell below is a live formula off INPUTS.  ·  ILLUSTRATIVE.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="211">
+  <si>
+    <t>Queenstown Harbor — Entitled-Lot (Capital-Light) Development Model</t>
+  </si>
+  <si>
+    <t>Entitle the land and sell ENTITLED lots; the builder funds the horizontal. Costs repaid, then a simple 50/50.  ·  Dynamic — live formulas off INPUTS.  ·  ILLUSTRATIVE.</t>
   </si>
   <si>
     <t>INPUTS  (edit these — everything below recalculates)</t>
@@ -53,22 +53,37 @@
     <t>blended; Queen Anne's Co. zoning to confirm</t>
   </si>
   <si>
-    <t>Finished lot price ($ / lot)</t>
-  </si>
-  <si>
-    <t>conservative — QAC lots avg ~$237K; new homes $600–705K</t>
-  </si>
-  <si>
-    <t>Horizontal site dev cost ($ / lot)</t>
-  </si>
-  <si>
-    <t>JV-funded; national benchmark $50–150K/acre</t>
-  </si>
-  <si>
-    <t>Soft costs ($)</t>
-  </si>
-  <si>
-    <t>entitlement, civil, environmental, legal, mgmt</t>
+    <t>Entitled lot price ($ / lot)</t>
+  </si>
+  <si>
+    <t>to a builder — ~finished $150K less the builder's ~$80K to finish</t>
+  </si>
+  <si>
+    <t>Entitlement / approvals ($)</t>
+  </si>
+  <si>
+    <t>planning, zoning, PUD</t>
+  </si>
+  <si>
+    <t>Civil engineering ($)</t>
+  </si>
+  <si>
+    <t>construction plans</t>
+  </si>
+  <si>
+    <t>Environmental studies ($)</t>
+  </si>
+  <si>
+    <t>wetlands, Critical Area</t>
+  </si>
+  <si>
+    <t>Legal / survey / title ($)</t>
+  </si>
+  <si>
+    <t>Project management ($)</t>
+  </si>
+  <si>
+    <t>consultants over the entitlement</t>
   </si>
   <si>
     <t>Marketing &amp; brokerage (% of revenue)</t>
@@ -77,37 +92,31 @@
     <t>lot sales</t>
   </si>
   <si>
-    <t>Contingency (% of hard cost)</t>
-  </si>
-  <si>
-    <t>on horizontal</t>
-  </si>
-  <si>
-    <t>Financing / interest carry ($)</t>
-  </si>
-  <si>
-    <t>development loan interest</t>
-  </si>
-  <si>
-    <t>Land basis — contributed ($)</t>
-  </si>
-  <si>
-    <t>allocated from $25M H6 purchase (~$29K/ac); appraisal to set</t>
-  </si>
-  <si>
-    <t>Development loan (% of total cost)</t>
-  </si>
-  <si>
-    <t>land-development / A&amp;D financing (60% LTC)</t>
-  </si>
-  <si>
-    <t>Preferred return</t>
-  </si>
-  <si>
-    <t>to equity, before promote</t>
-  </si>
-  <si>
-    <t>DEVELOPABLE LAND  →  LOTS</t>
+    <t>Contingency (% of soft cost)</t>
+  </si>
+  <si>
+    <t>on the soft costs</t>
+  </si>
+  <si>
+    <t>Financing / carry ($)</t>
+  </si>
+  <si>
+    <t>small bank line</t>
+  </si>
+  <si>
+    <t>Profit split — each side</t>
+  </si>
+  <si>
+    <t>50/50 after costs (no pref, no promote)</t>
+  </si>
+  <si>
+    <t>Josh ownership of property entity</t>
+  </si>
+  <si>
+    <t>→ Josh nets ~25% of profit</t>
+  </si>
+  <si>
+    <t>DEVELOPABLE LAND  →  ENTITLED LOTS</t>
   </si>
   <si>
     <t>Net developable land (acres)</t>
@@ -116,315 +125,252 @@
     <t>gross − conservation − golf − Critical Area</t>
   </si>
   <si>
+    <t>Entitled lots</t>
+  </si>
+  <si>
+    <t>net developable acres × density</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t>Gross entitled-lot revenue</t>
+  </si>
+  <si>
+    <t>entitled lots × entitled-lot price</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT COST  (SOFT ONLY — builder funds the horizontal)</t>
+  </si>
+  <si>
+    <t>Marketing &amp; brokerage</t>
+  </si>
+  <si>
+    <t>% of revenue</t>
+  </si>
+  <si>
+    <t>Soft costs (entitle the land)</t>
+  </si>
+  <si>
+    <t>entitlement + civil + env + legal + PM</t>
+  </si>
+  <si>
+    <t>Contingency</t>
+  </si>
+  <si>
+    <t>% of soft cost</t>
+  </si>
+  <si>
+    <t>Financing / carry</t>
+  </si>
+  <si>
+    <t>TOTAL DEVELOPMENT COST</t>
+  </si>
+  <si>
+    <t>what we fund (land contributed at ~zero basis)</t>
+  </si>
+  <si>
+    <t>PROFIT  &amp;  THE 50/50 SPLIT  (costs repaid first, then a straight deal)</t>
+  </si>
+  <si>
+    <t>Net profit</t>
+  </si>
+  <si>
+    <t>revenue − development cost</t>
+  </si>
+  <si>
+    <t>Profit margin (on revenue)</t>
+  </si>
+  <si>
+    <t>near-zero land basis</t>
+  </si>
+  <si>
+    <t>Return on cost</t>
+  </si>
+  <si>
+    <t>profit / development cost</t>
+  </si>
+  <si>
+    <t>→ Property / H entities (50%)</t>
+  </si>
+  <si>
+    <t>returns capital to Josh's investors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    of which Josh (~25% of profit)</t>
+  </si>
+  <si>
+    <t>Josh owns 50% of the property entity</t>
+  </si>
+  <si>
+    <t>→ Development company (50%)</t>
+  </si>
+  <si>
+    <t>Bob · JAL · partners — JAL earns a share + $15K/mo retainer</t>
+  </si>
+  <si>
+    <t>PROJECT CASH FLOW  (revenue × phasing − cost × phasing)</t>
+  </si>
+  <si>
+    <t>$ by year</t>
+  </si>
+  <si>
+    <t>Yr 0</t>
+  </si>
+  <si>
+    <t>Yr 1</t>
+  </si>
+  <si>
+    <t>Yr 2</t>
+  </si>
+  <si>
+    <t>Yr 3</t>
+  </si>
+  <si>
+    <t>Yr 4</t>
+  </si>
+  <si>
+    <t>Revenue phasing (entitled-lot sales)</t>
+  </si>
+  <si>
+    <t>Cost phasing (entitlement soft costs)</t>
+  </si>
+  <si>
+    <t>Entitled-lot revenue</t>
+  </si>
+  <si>
+    <t>Development cost</t>
+  </si>
+  <si>
+    <t>Net project cash flow</t>
+  </si>
+  <si>
+    <t>Project IRR (unlevered)</t>
+  </si>
+  <si>
+    <t>high — minimal capital on a near-zero-basis land</t>
+  </si>
+  <si>
+    <t>WHY CAPITAL-LIGHT  (entitled vs. finishing the lots ourselves)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Finished lots</t>
   </si>
   <si>
-    <t>net developable acres × density</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t>Gross lot revenue</t>
-  </si>
-  <si>
-    <t>finished lots × finished lot price</t>
-  </si>
-  <si>
-    <t>USES OF CAPITAL  (development budget)</t>
-  </si>
-  <si>
-    <t>Land contribution</t>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Development cost (capital deployed)</t>
+  </si>
+  <si>
+    <t>Finishing the lots adds ~$3.1M of profit but needs ~4.7× the capital and all the horizontal execution + absorption risk. Capital-light wins on return-on-cost and risk — and it's what the sponsor wants.</t>
+  </si>
+  <si>
+    <t>PROFIT SENSITIVITY  ($M — entitled lot price  ×  lot yield)</t>
+  </si>
+  <si>
+    <t>Entitled $/lot  /  lots</t>
+  </si>
+  <si>
+    <t>240 lots</t>
+  </si>
+  <si>
+    <t>280 lots</t>
+  </si>
+  <si>
+    <t>320 lots</t>
+  </si>
+  <si>
+    <t>$55K / lot</t>
+  </si>
+  <si>
+    <t>$70K / lot</t>
+  </si>
+  <si>
+    <t>$85K / lot</t>
+  </si>
+  <si>
+    <t>Net project profit ($M) across entitled-lot price × lot yield. Base = $70K × 280 lots (highlighted). 50% flows to the property (Josh's investor liquidity), 50% to the development company.</t>
+  </si>
+  <si>
+    <t>Illustrative and for discussion only. Capital-light entitled-lot basis: we fund only the soft costs to entitle the land and sell entitled lots; the builder funds the horizontal. Costs repaid first, then a straight 50/50 (no pref, no promote). The entitled-lot price is the key assumption — confirm against builder bids in diligence.</t>
+  </si>
+  <si>
+    <t>Queenstown Harbor — Phase 2: Hospitality (Hotel + Restaurants)</t>
+  </si>
+  <si>
+    <t>Hotel is a REQUIRED component (per Bob). VIVÂMEE-led resort; JAL leads capital formation.  ·  Dynamic.  ·  ILLUSTRATIVE.</t>
+  </si>
+  <si>
+    <t>Hotel — keys</t>
+  </si>
+  <si>
+    <t>boutique resort lodge</t>
+  </si>
+  <si>
+    <t>Hotel — cost / key ($)</t>
+  </si>
+  <si>
+    <t>HVS 2025: select ~$223K, full-service ~$409K</t>
+  </si>
+  <si>
+    <t>Hotel — ADR ($)</t>
+  </si>
+  <si>
+    <t>upscale Eastern Shore resort (weddings / golf)</t>
+  </si>
+  <si>
+    <t>Hotel — stabilized occupancy</t>
+  </si>
+  <si>
+    <t>leisure / resort</t>
+  </si>
+  <si>
+    <t>Hotel — total-revenue multiple (x rooms)</t>
+  </si>
+  <si>
+    <t>+ F&amp;B, banquets, spa</t>
+  </si>
+  <si>
+    <t>Hotel — NOI margin</t>
+  </si>
+  <si>
+    <t>stabilized</t>
+  </si>
+  <si>
+    <t>Restaurants — GLA (SF)</t>
+  </si>
+  <si>
+    <t>a suite of destination restaurants</t>
+  </si>
+  <si>
+    <t>Restaurants — build cost / SF ($)</t>
+  </si>
+  <si>
+    <t>full-service ~$555/SF</t>
+  </si>
+  <si>
+    <t>Restaurants — sales / SF ($)</t>
+  </si>
+  <si>
+    <t>upscale destination dining</t>
+  </si>
+  <si>
+    <t>Restaurants — NOI (% of sales)</t>
+  </si>
+  <si>
+    <t>rent / operating contribution</t>
+  </si>
+  <si>
+    <t>Land — hospitality parcel ($)</t>
   </si>
   <si>
     <t>contributed by Capital H6</t>
   </si>
   <si>
-    <t>Horizontal site development</t>
-  </si>
-  <si>
-    <t>lots × $/lot (roads, sewer, utilities)</t>
-  </si>
-  <si>
-    <t>Soft costs</t>
-  </si>
-  <si>
-    <t>entitlement, civil, env, legal</t>
-  </si>
-  <si>
-    <t>Marketing &amp; brokerage</t>
-  </si>
-  <si>
-    <t>% of revenue</t>
-  </si>
-  <si>
-    <t>Contingency</t>
-  </si>
-  <si>
-    <t>% of hard cost</t>
-  </si>
-  <si>
-    <t>Financing / interest carry</t>
-  </si>
-  <si>
-    <t>loan interest</t>
-  </si>
-  <si>
-    <t>TOTAL PROJECT COST</t>
-  </si>
-  <si>
-    <t>sum of uses</t>
-  </si>
-  <si>
-    <t>SOURCES OF CAPITAL  (capital stack)</t>
-  </si>
-  <si>
-    <t>Development loan (~60% LTC)</t>
-  </si>
-  <si>
-    <t>land-development financing</t>
-  </si>
-  <si>
-    <t>Land equity (contributed)</t>
-  </si>
-  <si>
-    <t>contributed land</t>
-  </si>
-  <si>
-    <t>Cash equity</t>
-  </si>
-  <si>
-    <t>balance — co-invest + LP raise</t>
-  </si>
-  <si>
-    <t>TOTAL CAPITAL</t>
-  </si>
-  <si>
-    <t>= total project cost</t>
-  </si>
-  <si>
-    <t>RETURNS</t>
-  </si>
-  <si>
-    <t>Net development profit</t>
-  </si>
-  <si>
-    <t>revenue − total cost</t>
-  </si>
-  <si>
-    <t>Profit margin (on revenue)</t>
-  </si>
-  <si>
-    <t>Profit on cost</t>
-  </si>
-  <si>
-    <t>Total equity (land + cash)</t>
-  </si>
-  <si>
-    <t>land contribution + cash equity</t>
-  </si>
-  <si>
-    <t>Distributable to equity (capital + profit)</t>
-  </si>
-  <si>
-    <t>returned to equity over the hold</t>
-  </si>
-  <si>
-    <t>Equity multiple</t>
-  </si>
-  <si>
-    <t>distributable / equity, levered</t>
-  </si>
-  <si>
-    <t>CASH-FLOW TIMING  (% by year — edit to re-phase; each row sums to 100%)</t>
-  </si>
-  <si>
-    <t>$ by year</t>
-  </si>
-  <si>
-    <t>Yr 0</t>
-  </si>
-  <si>
-    <t>Yr 1</t>
-  </si>
-  <si>
-    <t>Yr 2</t>
-  </si>
-  <si>
-    <t>Yr 3</t>
-  </si>
-  <si>
-    <t>Yr 4</t>
-  </si>
-  <si>
-    <t>Revenue phasing (lot sales)</t>
-  </si>
-  <si>
-    <t>Cost phasing (land/horizontal/soft)</t>
-  </si>
-  <si>
-    <t>Equity-draw phasing</t>
-  </si>
-  <si>
-    <t>Equity-distribution phasing</t>
-  </si>
-  <si>
-    <t>UNLEVERED PROJECT CASH FLOW  (revenue × phasing − cost × phasing)</t>
-  </si>
-  <si>
-    <t>Lot revenue</t>
-  </si>
-  <si>
-    <t>Total cost</t>
-  </si>
-  <si>
-    <t>Net project cash flow</t>
-  </si>
-  <si>
-    <t>Project IRR (unlevered)</t>
-  </si>
-  <si>
-    <t>lots sell Yr 2–4; land &amp; horizontal up front</t>
-  </si>
-  <si>
-    <t>LEVERED EQUITY CASH FLOW  (60% LTC development loan)</t>
-  </si>
-  <si>
-    <t>Equity drawn</t>
-  </si>
-  <si>
-    <t>Equity distributions</t>
-  </si>
-  <si>
-    <t>Project equity cash flow</t>
-  </si>
-  <si>
-    <t>Project equity IRR (levered)</t>
-  </si>
-  <si>
-    <t>equity ~$11.0M; unlevered project IRR ~24%</t>
-  </si>
-  <si>
-    <t>PROMOTE WATERFALL  (LP 90% / GP 10% · 8% pref · 80/20 to 15% · 70/30 to 20% · 60/40 above)</t>
-  </si>
-  <si>
-    <t>LP cash flow (after promote)</t>
-  </si>
-  <si>
-    <t>GP cash flow (co-invest + promote)</t>
-  </si>
-  <si>
-    <t>LP IRR (after promote)</t>
-  </si>
-  <si>
-    <t>what the equity investors earn</t>
-  </si>
-  <si>
-    <t>GP IRR (co-invest + carried interest)</t>
-  </si>
-  <si>
-    <t>sponsor group — Accountable Equity / Capital H6 / Bob / JAL + partners</t>
-  </si>
-  <si>
-    <t>GP net profit (co-invest + promote)</t>
-  </si>
-  <si>
-    <t>GP group total — JAL earns a share</t>
-  </si>
-  <si>
-    <t>LP / GP split is solved by the model's promote engine (an IRR-hurdle waterfall isn't a closed-form cell formula); the IRR / profit cells above are live over those rows.</t>
-  </si>
-  <si>
-    <t>LP IRR SENSITIVITY  (finished lot price  ×  LTC)</t>
-  </si>
-  <si>
-    <t>Lot price  /  LTC</t>
-  </si>
-  <si>
-    <t>$130K / lot</t>
-  </si>
-  <si>
-    <t>$150K / lot</t>
-  </si>
-  <si>
-    <t>$170K / lot</t>
-  </si>
-  <si>
-    <t>LP IRR after the 8% pref + tiered promote. Base = $150K lot / 60% LTC (highlighted). Each cell re-runs the full waterfall engine.</t>
-  </si>
-  <si>
-    <t>Illustrative and for discussion only. Figures compiled from public sources and independent research; subject to change and confirmation. Finished-lot model: the JV captures the homebuilder's development margin but takes horizontal execution risk and more capital than selling entitled (paper) lots.</t>
-  </si>
-  <si>
-    <t>Queenstown Harbor — Phase 2: Hospitality (Hotel + Restaurants)</t>
-  </si>
-  <si>
-    <t>VIVÂMEE-led resort; JAL leads capital formation.  ·  Dynamic — every cell below is a live formula off INPUTS.  ·  ILLUSTRATIVE.</t>
-  </si>
-  <si>
-    <t>Hotel — keys</t>
-  </si>
-  <si>
-    <t>boutique resort lodge</t>
-  </si>
-  <si>
-    <t>Hotel — cost / key ($)</t>
-  </si>
-  <si>
-    <t>HVS 2025: select ~$223K, full-service ~$409K</t>
-  </si>
-  <si>
-    <t>Hotel — ADR ($)</t>
-  </si>
-  <si>
-    <t>upscale Eastern Shore resort (weddings / golf)</t>
-  </si>
-  <si>
-    <t>Hotel — stabilized occupancy</t>
-  </si>
-  <si>
-    <t>leisure / resort</t>
-  </si>
-  <si>
-    <t>Hotel — total-revenue multiple (x rooms)</t>
-  </si>
-  <si>
-    <t>+ F&amp;B, banquets, spa</t>
-  </si>
-  <si>
-    <t>Hotel — NOI margin</t>
-  </si>
-  <si>
-    <t>stabilized</t>
-  </si>
-  <si>
-    <t>Restaurants — GLA (SF)</t>
-  </si>
-  <si>
-    <t>a suite of destination restaurants</t>
-  </si>
-  <si>
-    <t>Restaurants — build cost / SF ($)</t>
-  </si>
-  <si>
-    <t>full-service ~$555/SF</t>
-  </si>
-  <si>
-    <t>Restaurants — sales / SF ($)</t>
-  </si>
-  <si>
-    <t>upscale destination dining</t>
-  </si>
-  <si>
-    <t>Restaurants — NOI (% of sales)</t>
-  </si>
-  <si>
-    <t>rent / operating contribution</t>
-  </si>
-  <si>
-    <t>Land — hospitality parcel ($)</t>
-  </si>
-  <si>
     <t>Soft / FF&amp;E / pre-opening ($)</t>
   </si>
   <si>
@@ -455,7 +401,7 @@
     <t>Yr 2 opens partway through</t>
   </si>
   <si>
-    <t>HOTEL</t>
+    <t>HOTEL  (required component)</t>
   </si>
   <si>
     <t>Hotel development cost</t>
@@ -698,20 +644,21 @@
     <t>Build-to-core project IRR at 65% LTC, recap at stabilization (~Yr 4). Base = $4.65M NOI / 7.5% cap (highlighted). Each cell re-runs the engine.</t>
   </si>
   <si>
-    <t>Illustrative. Hospitality is an income / hold play: it develops to roughly cost, so the return is durable cash flow + appreciation (lower IRR than the Phase 1 land, longer hold) — unless you build to core and recap at stabilization. VIVÂMEE operates; JAL leads capital formation. The resort also lifts Phase 1 lot values. Subject to confirmation.</t>
+    <t>Illustrative. The hotel is a required component (per Bob); at Renault the plan is +100–200 rooms. Hospitality develops to ~cost (income/hold ~12% IRR) unless you build to core and recap at stabilization (~28%). VIVÂMEE operates; JAL leads capital formation. The resort also lifts the lot values. Subject to confirmation.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -769,6 +716,12 @@
     <font>
       <color rgb="FF0B163C"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0B163C"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -837,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -895,26 +848,41 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1256,10 +1224,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="12" customWidth="1"/>
@@ -1370,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="10">
-        <v>150000</v>
+        <v>70000</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>14</v>
@@ -1384,7 +1352,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="10">
-        <v>60000</v>
+        <v>1200000</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>16</v>
@@ -1398,7 +1366,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="10">
-        <v>2800000</v>
+        <v>1000000</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>18</v>
@@ -1411,8 +1379,8 @@
       <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="11">
-        <v>0.03</v>
+      <c r="B13" s="10">
+        <v>600000</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>20</v>
@@ -1421,29 +1389,23 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="11">
-        <v>0.07</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="10">
+        <v>500000</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="10">
+        <v>700000</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="B15" s="10">
-        <v>1400000</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1451,13 +1413,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="B16" s="10">
-        <v>4000000</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -1465,13 +1427,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B17" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -1479,133 +1441,131 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="10">
+        <v>300000</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="B18" s="11">
-        <v>0.08</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B20" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="7">
         <f>B5-B6-B7-B8</f>
         <v>140</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="13">
-        <f>B21*B9</f>
+      <c r="C23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="13">
+        <f>B23*B9</f>
         <v>280</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="14">
-        <f>B22*B10</f>
-        <v>42000000</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A27" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="10">
-        <f>B16</f>
-        <v>4000000</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="B27" s="14">
+        <f>B24*B10</f>
+        <v>19600000</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="10">
-        <f>B22*B11</f>
-        <v>16800000</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="10">
+        <f>B27*B16</f>
+        <v>588000</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="B30" s="10">
-        <f>B12</f>
-        <v>2800000</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -1613,14 +1573,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="10">
+        <f>B11+B12+B13+B14+B15</f>
+        <v>4000000</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B31" s="10">
-        <f>B25*B13</f>
-        <v>1260000</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -1628,14 +1588,14 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="10">
+        <f>B31*B17</f>
+        <v>400000</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B32" s="10">
-        <f>B29*B14</f>
-        <v>1176000</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -1643,14 +1603,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" s="10">
-        <f>B15</f>
-        <v>1400000</v>
+        <f>B18</f>
+        <v>300000</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -1658,14 +1618,14 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B34" s="16">
-        <f>SUM(B28:B33)</f>
-        <v>27436000</v>
+        <f>B31+B30+B32+B33</f>
+        <v>5288000</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1673,7 +1633,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -1682,15 +1642,15 @@
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="10">
-        <f>B34*B17</f>
-        <v>16461600</v>
+      <c r="A37" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="14">
+        <f>B27-B34</f>
+        <v>14312000</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -1698,712 +1658,402 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="10">
-        <f>B16</f>
-        <v>4000000</v>
+        <v>55</v>
+      </c>
+      <c r="B38" s="11">
+        <f>B37/B27</f>
+        <v>0.730204081632653</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="10">
-        <f>B34-B37-B38</f>
-        <v>6974400</v>
+      <c r="A39" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="17">
+        <f>B37/B34</f>
+        <v>2.706505295007564</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="16">
-        <f>SUM(B37:B39)</f>
-        <v>27436000</v>
+      <c r="A40" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="10">
+        <f>B37*B19</f>
+        <v>7156000</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="10">
+        <f>B40*B20</f>
+        <v>3578000</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+    </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="B42" s="14">
+        <f>B37*(1-B19)</f>
+        <v>7156000</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="14">
-        <f>B25-B34</f>
-        <v>14564000</v>
-      </c>
-      <c r="C43" s="8" t="s">
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B44" s="11">
-        <f>B43/B25</f>
-        <v>0.34676190476190477</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="B45" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="11">
-        <f>B43/B34</f>
-        <v>0.5308353987461729</v>
+      <c r="C45" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="10">
-        <f>B38+B39</f>
-        <v>10974400</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="B46" s="20">
+        <v>0</v>
+      </c>
+      <c r="C46" s="20">
+        <v>0</v>
+      </c>
+      <c r="D46" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="F46" s="20">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="10">
-        <f>B46+B43</f>
-        <v>25538400</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+        <v>73</v>
+      </c>
+      <c r="B47" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="C47" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="D47" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="E47" s="20">
+        <v>0.07</v>
+      </c>
+      <c r="F47" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" s="17">
-        <f>B47/B46</f>
-        <v>2.327088496865432</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="A48" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="21">
+        <f>$B$27*B46</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="21">
+        <f>$B$27*C46</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <f>$B$27*D46</f>
+        <v>4900000</v>
+      </c>
+      <c r="E48" s="21">
+        <f>$B$27*E46</f>
+        <v>7840000</v>
+      </c>
+      <c r="F48" s="21">
+        <f>$B$27*F46</f>
+        <v>6860000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="21">
+        <f>-$B$34*B47</f>
+        <v>-1586400</v>
+      </c>
+      <c r="C49" s="21">
+        <f>-$B$34*C47</f>
+        <v>-2379600</v>
+      </c>
+      <c r="D49" s="21">
+        <f>-$B$34*D47</f>
+        <v>-951840</v>
+      </c>
+      <c r="E49" s="21">
+        <f>-$B$34*E47</f>
+        <v>-370160.00000000006</v>
+      </c>
+      <c r="F49" s="21">
+        <f>-$B$34*F47</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="14">
+        <f>B48+B49</f>
+        <v>-1586400</v>
+      </c>
+      <c r="C50" s="14">
+        <f>C48+C49</f>
+        <v>-2379600</v>
+      </c>
+      <c r="D50" s="14">
+        <f>D48+D49</f>
+        <v>3948160</v>
+      </c>
+      <c r="E50" s="14">
+        <f>E48+E49</f>
+        <v>7469840</v>
+      </c>
+      <c r="F50" s="14">
+        <f>F48+F49</f>
+        <v>6860000</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="B51" s="22">
+        <f>IRR(B50:F50)</f>
+        <v>0.8626036987758889</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="23" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="B54" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B52" s="20">
-        <v>0</v>
-      </c>
-      <c r="C52" s="20">
-        <v>0</v>
-      </c>
-      <c r="D52" s="20">
-        <v>0.19047619047619047</v>
-      </c>
-      <c r="E52" s="20">
-        <v>0.40476190476190477</v>
-      </c>
-      <c r="F52" s="20">
-        <v>0.40476190476190477</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B53" s="20">
-        <v>0.22</v>
-      </c>
-      <c r="C53" s="20">
-        <v>0.38</v>
-      </c>
-      <c r="D53" s="20">
-        <v>0.36</v>
-      </c>
-      <c r="E53" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="F53" s="20">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="B55" s="14">
+        <v>19600000</v>
+      </c>
+      <c r="C55" s="21">
+        <v>42000000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="20">
-        <v>0.607</v>
-      </c>
-      <c r="C54" s="20">
-        <v>0.393</v>
-      </c>
-      <c r="D54" s="20">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20">
-        <v>0</v>
-      </c>
-      <c r="F54" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="B56" s="14">
+        <v>5288000</v>
+      </c>
+      <c r="C56" s="21">
+        <v>24636000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="14">
+        <v>14312000</v>
+      </c>
+      <c r="C57" s="21">
+        <v>17364000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="17">
+        <v>2.706505295007564</v>
+      </c>
+      <c r="C58" s="25">
+        <v>0.7048222113979542</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="20">
-        <v>0</v>
-      </c>
-      <c r="C55" s="20">
-        <v>0</v>
-      </c>
-      <c r="D55" s="20">
-        <v>0.088</v>
-      </c>
-      <c r="E55" s="20">
-        <v>0.307</v>
-      </c>
-      <c r="F55" s="20">
-        <v>0.605</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="21">
-        <f>$B$25*B52</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="21">
-        <f>$B$25*C52</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="21">
-        <f>$B$25*D52</f>
-        <v>8000000</v>
-      </c>
-      <c r="E59" s="21">
-        <f>$B$25*E52</f>
-        <v>17000000</v>
-      </c>
-      <c r="F59" s="21">
-        <f>$B$25*F52</f>
-        <v>17000000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="B62" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="21">
-        <f>-$B$34*B53</f>
-        <v>-6035920</v>
-      </c>
-      <c r="C60" s="21">
-        <f>-$B$34*C53</f>
-        <v>-10425680</v>
-      </c>
-      <c r="D60" s="21">
-        <f>-$B$34*D53</f>
-        <v>-9876960</v>
-      </c>
-      <c r="E60" s="21">
-        <f>-$B$34*E53</f>
-        <v>-823080</v>
-      </c>
-      <c r="F60" s="21">
-        <f>-$B$34*F53</f>
-        <v>-274360</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+      <c r="C62" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="14">
-        <f>B59+B60</f>
-        <v>-6035920</v>
-      </c>
-      <c r="C61" s="14">
-        <f>C59+C60</f>
-        <v>-10425680</v>
-      </c>
-      <c r="D61" s="14">
-        <f>D59+D60</f>
-        <v>-1876960</v>
-      </c>
-      <c r="E61" s="14">
-        <f>E59+E60</f>
-        <v>16176920</v>
-      </c>
-      <c r="F61" s="14">
-        <f>F59+F60</f>
-        <v>16725640</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
+      <c r="D62" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="22">
-        <f>IRR(B61:F61)</f>
-        <v>0.23697429468401643</v>
-      </c>
-      <c r="C62" s="8" t="s">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="B63" s="29">
+        <v>8.104</v>
+      </c>
+      <c r="C63" s="29">
+        <v>10.238</v>
+      </c>
+      <c r="D63" s="29">
+        <v>12.372</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>80</v>
+      <c r="B64" s="29">
+        <v>11.596</v>
+      </c>
+      <c r="C64" s="30">
+        <v>14.312</v>
+      </c>
+      <c r="D64" s="29">
+        <v>17.028</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="29">
+        <v>15.088</v>
+      </c>
+      <c r="C65" s="29">
+        <v>18.386</v>
+      </c>
+      <c r="D65" s="29">
+        <v>21.684</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" s="21">
-        <f>-$B$46*B54</f>
-        <v>-6661460.8</v>
-      </c>
-      <c r="C66" s="21">
-        <f>-$B$46*C54</f>
-        <v>-4312939.2</v>
-      </c>
-      <c r="D66" s="21">
-        <f>-$B$46*D54</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="21">
-        <f>-$B$46*E54</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="21">
-        <f>-$B$46*F54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A66" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="21">
-        <f>$B$47*B55</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="21">
-        <f>$B$47*C55</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="21">
-        <f>$B$47*D55</f>
-        <v>2247379.1999999997</v>
-      </c>
-      <c r="E67" s="21">
-        <f>$B$47*E55</f>
-        <v>7840288.8</v>
-      </c>
-      <c r="F67" s="21">
-        <f>$B$47*F55</f>
-        <v>15450732</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="68" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="B68" s="10">
-        <f>B66+B67</f>
-        <v>-6661460.8</v>
-      </c>
-      <c r="C68" s="10">
-        <f>C66+C67</f>
-        <v>-4312939.2</v>
-      </c>
-      <c r="D68" s="10">
-        <f>D66+D67</f>
-        <v>2247379.1999999997</v>
-      </c>
-      <c r="E68" s="10">
-        <f>E66+E67</f>
-        <v>7840288.8</v>
-      </c>
-      <c r="F68" s="10">
-        <f>F66+F67</f>
-        <v>15450732</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B69" s="22">
-        <f>IRR(B68:F68)</f>
-        <v>0.31384809341597164</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B73" s="21">
-        <v>-5995315</v>
-      </c>
-      <c r="C73" s="21">
-        <v>-3881645</v>
-      </c>
-      <c r="D73" s="21">
-        <v>2022641</v>
-      </c>
-      <c r="E73" s="21">
-        <v>7056260</v>
-      </c>
-      <c r="F73" s="21">
-        <v>11235772</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" s="21">
-        <v>-666146</v>
-      </c>
-      <c r="C74" s="21">
-        <v>-431294</v>
-      </c>
-      <c r="D74" s="21">
-        <v>224738</v>
-      </c>
-      <c r="E74" s="21">
-        <v>784029</v>
-      </c>
-      <c r="F74" s="21">
-        <v>4214960</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="22">
-        <f>IRR(B73:F73)</f>
-        <v>0.26841642110322594</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B76" s="11">
-        <f>IRR(B74:F74)</f>
-        <v>0.5930774883918588</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B77" s="10">
-        <f>SUM(B74:F74)</f>
-        <v>4126286</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B81" s="24">
-        <v>0.55</v>
-      </c>
-      <c r="C81" s="24">
-        <v>0.6</v>
-      </c>
-      <c r="D81" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="E81" s="24">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B82" s="26">
-        <v>0.18078353298753924</v>
-      </c>
-      <c r="C82" s="26">
-        <v>0.19735068232227648</v>
-      </c>
-      <c r="D82" s="26">
-        <v>0.21556470054605692</v>
-      </c>
-      <c r="E82" s="26">
-        <v>0.23872937985286258</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B83" s="26">
-        <v>0.24776127543856818</v>
-      </c>
-      <c r="C83" s="27">
-        <v>0.26841642110322594</v>
-      </c>
-      <c r="D83" s="26">
-        <v>0.2942311832200314</v>
-      </c>
-      <c r="E83" s="26">
-        <v>0.3275162111848672</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="B84" s="26">
-        <v>0.3066500722851123</v>
-      </c>
-      <c r="C84" s="26">
-        <v>0.33287240798168527</v>
-      </c>
-      <c r="D84" s="26">
-        <v>0.36543747436242235</v>
-      </c>
-      <c r="E84" s="26">
-        <v>0.4065234048048615</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-    </row>
-    <row r="87" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B87" s="28"/>
-      <c r="C87" s="28"/>
-      <c r="D87" s="28"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="28"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="34">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -2414,16 +2064,15 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
@@ -2433,18 +2082,12 @@
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A68:F68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2464,7 +2107,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2474,7 +2117,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2494,13 +2137,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2508,13 +2151,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2522,13 +2165,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2536,13 +2179,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2550,13 +2193,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="29">
+        <v>105</v>
+      </c>
+      <c r="B9" s="32">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2564,13 +2207,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2578,13 +2221,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2592,13 +2235,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2606,13 +2249,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2620,13 +2263,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2634,13 +2277,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -2648,7 +2291,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2656,13 +2299,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2670,7 +2313,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2678,7 +2321,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2686,7 +2329,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -2694,13 +2337,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B21" s="11">
         <v>0.5</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2708,13 +2351,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B22" s="11">
         <v>0.5</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -2722,7 +2365,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2732,14 +2375,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B25" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2747,14 +2390,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B26" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2762,14 +2405,14 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B27" s="10">
         <f>B26*B9</f>
         <v>9052000</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -2777,14 +2420,14 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B28" s="14">
         <f>B27*B10</f>
         <v>2806120</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -2792,7 +2435,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2802,14 +2445,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B31" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2817,14 +2460,14 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B32" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -2832,14 +2475,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B33" s="14">
         <f>B32*B14</f>
         <v>1008000</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2847,7 +2490,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2857,14 +2500,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B36" s="16">
         <f>B25+B31+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2872,14 +2515,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="B37" s="16">
         <f>B28+B33</f>
         <v>3814120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2887,14 +2530,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="B38" s="11">
         <f>B37/B36</f>
         <v>0.08115148936170213</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2902,14 +2545,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B39" s="10">
         <f>B36*B18</f>
         <v>28200000</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2917,14 +2560,14 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B40" s="10">
         <f>B36-B39</f>
         <v>18800000</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
@@ -2932,14 +2575,14 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="B41" s="10">
         <f>B37-B39*B19</f>
         <v>1840119.9999999998</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -2947,14 +2590,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B42" s="11">
         <f>B41/B40</f>
         <v>0.09787872340425531</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2962,7 +2605,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2972,14 +2615,14 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B45" s="10">
         <f>B37*(1+B20)^4</f>
         <v>4292825.6623972</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
@@ -2987,14 +2630,14 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B46" s="10">
         <f>B45/B17</f>
         <v>53660320.779965</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
@@ -3002,14 +2645,14 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B47" s="10">
         <f>B46-B39</f>
         <v>25460320.779965</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -3017,7 +2660,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -3027,7 +2670,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B50" s="21">
         <f>-B40*B21</f>
@@ -3036,7 +2679,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B51" s="21">
         <f>-B40*(1-B21)</f>
@@ -3045,7 +2688,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B52" s="21">
         <f>B41*B22</f>
@@ -3054,7 +2697,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B53" s="21">
         <f>B41</f>
@@ -3063,7 +2706,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B54" s="21">
         <f>B41*(1+B20)</f>
@@ -3072,7 +2715,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="B55" s="21">
         <f>B41*(1+B20)^2</f>
@@ -3081,7 +2724,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B56" s="21">
         <f>B41*(1+B20)^3</f>
@@ -3090,7 +2733,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B57" s="21">
         <f>B41*(1+B20)^4+B47</f>
@@ -3099,14 +2742,14 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B58" s="17">
         <f>SUM(B52:B57)/-(B50+B51)</f>
         <v>1.9228631790777764</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -3114,14 +2757,14 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B59" s="22">
         <f>IRR(B50:B57)</f>
         <v>0.12039129900378642</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -3129,7 +2772,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -3139,13 +2782,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B62" s="11">
         <v>0.22</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -3153,14 +2796,14 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B63" s="14">
         <f>B37*(1+B62)</f>
         <v>4653226.399999999</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -3168,13 +2811,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B64" s="11">
         <v>0.075</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -3182,13 +2825,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B65" s="11">
         <v>0.65</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -3196,13 +2839,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B66" s="11">
         <v>0.4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -3210,14 +2853,14 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B67" s="11">
         <f>B63/B36</f>
         <v>0.09900481702127659</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -3225,14 +2868,14 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B68" s="10">
         <f>B63/B64</f>
         <v>62043018.666666664</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -3240,14 +2883,14 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B69" s="10">
         <f>B36*B65</f>
         <v>30550000</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
@@ -3255,14 +2898,14 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B70" s="10">
         <f>B36-B69</f>
         <v>16450000</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
@@ -3270,14 +2913,14 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B71" s="10">
         <f>B63-B69*B19</f>
         <v>2514726.3999999994</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -3285,14 +2928,14 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B72" s="10">
         <f>B68-B69</f>
         <v>31493018.666666664</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
@@ -3300,7 +2943,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3310,7 +2953,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B75" s="21">
         <f>-B70*B21</f>
@@ -3319,7 +2962,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B76" s="21">
         <f>-B70*(1-B21)</f>
@@ -3328,7 +2971,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B77" s="21">
         <f>B71*B66</f>
@@ -3337,7 +2980,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B78" s="21">
         <f>B71</f>
@@ -3346,7 +2989,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B79" s="21">
         <f>B71+B72</f>
@@ -3355,14 +2998,14 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B80" s="17">
         <f>SUM(B77:B79)/-(B75+B76)</f>
         <v>2.281359393718338</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -3370,14 +3013,14 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B81" s="22">
         <f>IRR(B75:B79)</f>
         <v>0.27563551751308235</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -3385,7 +3028,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3394,76 +3037,76 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="B84" s="30">
+      <c r="A84" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B84" s="33">
         <v>0.07</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C84" s="33">
         <v>0.075</v>
       </c>
-      <c r="D84" s="30">
+      <c r="D84" s="33">
         <v>0.08</v>
       </c>
-      <c r="E84" s="30">
+      <c r="E84" s="33">
         <v>0.085</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B85" s="26">
+      <c r="A85" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" s="34">
         <v>0.2413590494653527</v>
       </c>
-      <c r="C85" s="26">
+      <c r="C85" s="34">
         <v>0.1981010805160578</v>
       </c>
-      <c r="D85" s="26">
+      <c r="D85" s="34">
         <v>0.15643182900562425</v>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="34">
         <v>0.11594756701498155</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B86" s="26">
+      <c r="A86" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B86" s="34">
         <v>0.3166711576166231</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="35">
         <v>0.27563551751308235</v>
       </c>
-      <c r="D86" s="26">
+      <c r="D86" s="34">
         <v>0.2365089547947662</v>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="34">
         <v>0.1989302587607228</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="B87" s="26">
+      <c r="A87" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" s="34">
         <v>0.3879656267349022</v>
       </c>
-      <c r="C87" s="26">
+      <c r="C87" s="34">
         <v>0.3484741336946878</v>
       </c>
-      <c r="D87" s="26">
+      <c r="D87" s="34">
         <v>0.31109801406577653</v>
       </c>
-      <c r="E87" s="26">
+      <c r="E87" s="34">
         <v>0.2754915069098355</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -3472,14 +3115,14 @@
       <c r="F88" s="8"/>
     </row>
     <row r="90" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="B90" s="28"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28"/>
+      <c r="A90" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
+      <c r="D90" s="31"/>
+      <c r="E90" s="31"/>
+      <c r="F90" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="49">

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="215">
   <si>
     <t>Queenstown Harbor — Entitled-Lot (Capital-Light) Development Model</t>
   </si>
@@ -116,6 +116,12 @@
     <t>→ Josh nets ~25% of profit</t>
   </si>
   <si>
+    <t>JAL share of the dev co</t>
+  </si>
+  <si>
+    <t>sweat equity — ~1/3 of the dev-co 50% (~17% of profit)</t>
+  </si>
+  <si>
     <t>DEVELOPABLE LAND  →  ENTITLED LOTS</t>
   </si>
   <si>
@@ -206,7 +212,13 @@
     <t>→ Development company (50%)</t>
   </si>
   <si>
-    <t>Bob · JAL · partners — JAL earns a share + $15K/mo retainer</t>
+    <t>Accountable Equity / Capital H6 · Bob · JAL · partners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    of which JAL (~1/3 of dev co)</t>
+  </si>
+  <si>
+    <t>sweat equity — separate from any placement fee or co-invest; + $15K/mo retainer</t>
   </si>
   <si>
     <t>PROJECT CASH FLOW  (revenue × phasing − cost × phasing)</t>
@@ -1224,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1481,38 +1493,37 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="B21" s="11">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="7">
-        <f>B5-B6-B7-B8</f>
-        <v>140</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="A23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="13">
-        <f>B23*B9</f>
-        <v>280</v>
+      <c r="B24" s="7">
+        <f>B5-B6-B7-B8</f>
+        <v>140</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>38</v>
@@ -1521,63 +1532,63 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="B25" s="13">
+        <f>B24*B9</f>
+        <v>280</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="14">
-        <f>B24*B10</f>
+      <c r="A27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="14">
+        <f>B25*B10</f>
         <v>19600000</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="C28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="10">
-        <f>B27*B16</f>
-        <v>588000</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="A30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B31" s="10">
-        <f>B11+B12+B13+B14+B15</f>
-        <v>4000000</v>
+        <f>B28*B16</f>
+        <v>588000</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>46</v>
@@ -1591,8 +1602,8 @@
         <v>47</v>
       </c>
       <c r="B32" s="10">
-        <f>B31*B17</f>
-        <v>400000</v>
+        <f>B11+B12+B13+B14+B15</f>
+        <v>4000000</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>48</v>
@@ -1606,63 +1617,63 @@
         <v>49</v>
       </c>
       <c r="B33" s="10">
-        <f>B18</f>
-        <v>300000</v>
+        <f>B32*B17</f>
+        <v>400000</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="16">
-        <f>B31+B30+B32+B33</f>
-        <v>5288000</v>
+      <c r="A34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="10">
+        <f>B18</f>
+        <v>300000</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="B35" s="16">
+        <f>B32+B31+B33+B34</f>
+        <v>5288000</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="14">
-        <f>B27-B34</f>
+      <c r="A37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="14">
+        <f>B28-B35</f>
         <v>14312000</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="11">
-        <f>B37/B27</f>
-        <v>0.730204081632653</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>56</v>
@@ -1672,12 +1683,12 @@
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="17">
-        <f>B37/B34</f>
-        <v>2.706505295007564</v>
+      <c r="B39" s="11">
+        <f>B38/B28</f>
+        <v>0.730204081632653</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>58</v>
@@ -1690,9 +1701,9 @@
       <c r="A40" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="10">
-        <f>B37*B19</f>
-        <v>7156000</v>
+      <c r="B40" s="17">
+        <f>B38/B35</f>
+        <v>2.706505295007564</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>60</v>
@@ -1702,12 +1713,12 @@
       <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B41" s="10">
-        <f>B40*B20</f>
-        <v>3578000</v>
+        <f>B38*B19</f>
+        <v>7156000</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>62</v>
@@ -1717,12 +1728,12 @@
       <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="14">
-        <f>B37*(1-B19)</f>
-        <v>7156000</v>
+      <c r="B42" s="10">
+        <f>B41*B20</f>
+        <v>3578000</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>64</v>
@@ -1731,329 +1742,359 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="14">
+        <f>B38*(1-B19)</f>
+        <v>7156000</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+    </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="19" t="s">
+      <c r="A44" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="B44" s="10">
+        <f>B43*B21</f>
+        <v>2385333.333333333</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="B47" s="19" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="C47" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="20">
-        <v>0</v>
-      </c>
-      <c r="C46" s="20">
-        <v>0</v>
-      </c>
-      <c r="D46" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="E46" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="D47" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="C47" s="20">
-        <v>0.45</v>
-      </c>
-      <c r="D47" s="20">
-        <v>0.18</v>
-      </c>
-      <c r="E47" s="20">
-        <v>0.07</v>
-      </c>
-      <c r="F47" s="20">
-        <v>0</v>
+      <c r="E47" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B48" s="21">
-        <f>$B$27*B46</f>
+        <v>76</v>
+      </c>
+      <c r="B48" s="20">
         <v>0</v>
       </c>
-      <c r="C48" s="21">
-        <f>$B$27*C46</f>
+      <c r="C48" s="20">
         <v>0</v>
       </c>
-      <c r="D48" s="21">
-        <f>$B$27*D46</f>
-        <v>4900000</v>
-      </c>
-      <c r="E48" s="21">
-        <f>$B$27*E46</f>
-        <v>7840000</v>
-      </c>
-      <c r="F48" s="21">
-        <f>$B$27*F46</f>
-        <v>6860000</v>
+      <c r="D48" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="E48" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="F48" s="20">
+        <v>0.35</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="21">
-        <f>-$B$34*B47</f>
+        <v>77</v>
+      </c>
+      <c r="B49" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="C49" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="D49" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="E49" s="20">
+        <v>0.07</v>
+      </c>
+      <c r="F49" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="21">
+        <f>$B$28*B48</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="21">
+        <f>$B$28*C48</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="21">
+        <f>$B$28*D48</f>
+        <v>4900000</v>
+      </c>
+      <c r="E50" s="21">
+        <f>$B$28*E48</f>
+        <v>7840000</v>
+      </c>
+      <c r="F50" s="21">
+        <f>$B$28*F48</f>
+        <v>6860000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="21">
+        <f>-$B$35*B49</f>
         <v>-1586400</v>
       </c>
-      <c r="C49" s="21">
-        <f>-$B$34*C47</f>
+      <c r="C51" s="21">
+        <f>-$B$35*C49</f>
         <v>-2379600</v>
       </c>
-      <c r="D49" s="21">
-        <f>-$B$34*D47</f>
+      <c r="D51" s="21">
+        <f>-$B$35*D49</f>
         <v>-951840</v>
       </c>
-      <c r="E49" s="21">
-        <f>-$B$34*E47</f>
+      <c r="E51" s="21">
+        <f>-$B$35*E49</f>
         <v>-370160.00000000006</v>
       </c>
-      <c r="F49" s="21">
-        <f>-$B$34*F47</f>
+      <c r="F51" s="21">
+        <f>-$B$35*F49</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" s="14">
-        <f>B48+B49</f>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="14">
+        <f>B50+B51</f>
         <v>-1586400</v>
       </c>
-      <c r="C50" s="14">
-        <f>C48+C49</f>
+      <c r="C52" s="14">
+        <f>C50+C51</f>
         <v>-2379600</v>
       </c>
-      <c r="D50" s="14">
-        <f>D48+D49</f>
+      <c r="D52" s="14">
+        <f>D50+D51</f>
         <v>3948160</v>
       </c>
-      <c r="E50" s="14">
-        <f>E48+E49</f>
+      <c r="E52" s="14">
+        <f>E50+E51</f>
         <v>7469840</v>
       </c>
-      <c r="F50" s="14">
-        <f>F48+F49</f>
+      <c r="F52" s="14">
+        <f>F50+F51</f>
         <v>6860000</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" s="22">
-        <f>IRR(B50:F50)</f>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="22">
+        <f>IRR(B52:F52)</f>
         <v>0.8626036987758889</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="C53" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B55" s="14">
-        <v>19600000</v>
-      </c>
-      <c r="C55" s="21">
-        <v>42000000</v>
-      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="14">
-        <v>5288000</v>
-      </c>
-      <c r="C56" s="21">
-        <v>24636000</v>
+      <c r="A56" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="B57" s="14">
-        <v>14312000</v>
+        <v>19600000</v>
       </c>
       <c r="C57" s="21">
-        <v>17364000</v>
+        <v>42000000</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="17">
+        <v>87</v>
+      </c>
+      <c r="B58" s="14">
+        <v>5288000</v>
+      </c>
+      <c r="C58" s="21">
+        <v>24636000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="14">
+        <v>14312000</v>
+      </c>
+      <c r="C59" s="21">
+        <v>17364000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="17">
         <v>2.706505295007564</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C60" s="25">
         <v>0.7048222113979542</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" s="27" t="s">
+      <c r="A61" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="28" t="s">
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="29">
-        <v>8.104</v>
-      </c>
-      <c r="C63" s="29">
-        <v>10.238</v>
-      </c>
-      <c r="D63" s="29">
-        <v>12.372</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="28" t="s">
+      <c r="B64" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="29">
-        <v>11.596</v>
-      </c>
-      <c r="C64" s="30">
-        <v>14.312</v>
-      </c>
-      <c r="D64" s="29">
-        <v>17.028</v>
+      <c r="C64" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B65" s="29">
+        <v>8.104</v>
+      </c>
+      <c r="C65" s="29">
+        <v>10.238</v>
+      </c>
+      <c r="D65" s="29">
+        <v>12.372</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="29">
+        <v>11.596</v>
+      </c>
+      <c r="C66" s="30">
+        <v>14.312</v>
+      </c>
+      <c r="D66" s="29">
+        <v>17.028</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="29">
         <v>15.088</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C67" s="29">
         <v>18.386</v>
       </c>
-      <c r="D65" s="29">
+      <c r="D67" s="29">
         <v>21.684</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="68" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+    </row>
+    <row r="70" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -2070,24 +2111,26 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A70:F70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2107,7 +2150,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2117,7 +2160,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2137,13 +2180,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2151,13 +2194,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2165,13 +2208,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2179,13 +2222,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2193,13 +2236,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B9" s="32">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2207,13 +2250,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2221,13 +2264,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2235,13 +2278,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2249,13 +2292,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2263,13 +2306,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2277,13 +2320,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -2291,7 +2334,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2299,13 +2342,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2313,7 +2356,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2321,7 +2364,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2329,7 +2372,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -2337,13 +2380,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B21" s="11">
         <v>0.5</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2351,13 +2394,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B22" s="11">
         <v>0.5</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -2365,7 +2408,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2375,14 +2418,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B25" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2390,14 +2433,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2405,14 +2448,14 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B27" s="10">
         <f>B26*B9</f>
         <v>9052000</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -2420,14 +2463,14 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B28" s="14">
         <f>B27*B10</f>
         <v>2806120</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -2435,7 +2478,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2445,14 +2488,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B31" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2460,14 +2503,14 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B32" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -2475,14 +2518,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B33" s="14">
         <f>B32*B14</f>
         <v>1008000</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2490,7 +2533,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2500,14 +2543,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B36" s="16">
         <f>B25+B31+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2515,14 +2558,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B37" s="16">
         <f>B28+B33</f>
         <v>3814120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2530,14 +2573,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B38" s="11">
         <f>B37/B36</f>
         <v>0.08115148936170213</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2545,14 +2588,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B39" s="10">
         <f>B36*B18</f>
         <v>28200000</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2560,14 +2603,14 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B40" s="10">
         <f>B36-B39</f>
         <v>18800000</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
@@ -2575,14 +2618,14 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B41" s="10">
         <f>B37-B39*B19</f>
         <v>1840119.9999999998</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -2590,14 +2633,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B42" s="11">
         <f>B41/B40</f>
         <v>0.09787872340425531</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2605,7 +2648,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2615,14 +2658,14 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B45" s="10">
         <f>B37*(1+B20)^4</f>
         <v>4292825.6623972</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
@@ -2630,14 +2673,14 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B46" s="10">
         <f>B45/B17</f>
         <v>53660320.779965</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
@@ -2645,14 +2688,14 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B47" s="10">
         <f>B46-B39</f>
         <v>25460320.779965</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -2660,7 +2703,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2670,7 +2713,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B50" s="21">
         <f>-B40*B21</f>
@@ -2679,7 +2722,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B51" s="21">
         <f>-B40*(1-B21)</f>
@@ -2688,7 +2731,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B52" s="21">
         <f>B41*B22</f>
@@ -2697,7 +2740,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B53" s="21">
         <f>B41</f>
@@ -2706,7 +2749,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B54" s="21">
         <f>B41*(1+B20)</f>
@@ -2715,7 +2758,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B55" s="21">
         <f>B41*(1+B20)^2</f>
@@ -2724,7 +2767,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B56" s="21">
         <f>B41*(1+B20)^3</f>
@@ -2733,7 +2776,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B57" s="21">
         <f>B41*(1+B20)^4+B47</f>
@@ -2742,14 +2785,14 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B58" s="17">
         <f>SUM(B52:B57)/-(B50+B51)</f>
         <v>1.9228631790777764</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -2757,14 +2800,14 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B59" s="22">
         <f>IRR(B50:B57)</f>
         <v>0.12039129900378642</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -2772,7 +2815,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2782,13 +2825,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B62" s="11">
         <v>0.22</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -2796,14 +2839,14 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B63" s="14">
         <f>B37*(1+B62)</f>
         <v>4653226.399999999</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -2811,13 +2854,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B64" s="11">
         <v>0.075</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -2825,13 +2868,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B65" s="11">
         <v>0.65</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -2839,13 +2882,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B66" s="11">
         <v>0.4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -2853,14 +2896,14 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B67" s="11">
         <f>B63/B36</f>
         <v>0.09900481702127659</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -2868,14 +2911,14 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B68" s="10">
         <f>B63/B64</f>
         <v>62043018.666666664</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -2883,14 +2926,14 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B69" s="10">
         <f>B36*B65</f>
         <v>30550000</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
@@ -2898,14 +2941,14 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B70" s="10">
         <f>B36-B69</f>
         <v>16450000</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
@@ -2913,14 +2956,14 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B71" s="10">
         <f>B63-B69*B19</f>
         <v>2514726.3999999994</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -2928,14 +2971,14 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B72" s="10">
         <f>B68-B69</f>
         <v>31493018.666666664</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
@@ -2943,7 +2986,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2953,7 +2996,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B75" s="21">
         <f>-B70*B21</f>
@@ -2962,7 +3005,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B76" s="21">
         <f>-B70*(1-B21)</f>
@@ -2971,7 +3014,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B77" s="21">
         <f>B71*B66</f>
@@ -2980,7 +3023,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B78" s="21">
         <f>B71</f>
@@ -2989,7 +3032,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B79" s="21">
         <f>B71+B72</f>
@@ -2998,14 +3041,14 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B80" s="17">
         <f>SUM(B77:B79)/-(B75+B76)</f>
         <v>2.281359393718338</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -3013,14 +3056,14 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B81" s="22">
         <f>IRR(B75:B79)</f>
         <v>0.27563551751308235</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -3028,7 +3071,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3038,7 +3081,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B84" s="33">
         <v>0.07</v>
@@ -3055,7 +3098,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B85" s="34">
         <v>0.2413590494653527</v>
@@ -3072,7 +3115,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B86" s="34">
         <v>0.3166711576166231</v>
@@ -3089,7 +3132,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B87" s="34">
         <v>0.3879656267349022</v>
@@ -3106,7 +3149,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -3116,7 +3159,7 @@
     </row>
     <row r="90" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="31" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B90" s="31"/>
       <c r="C90" s="31"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="219">
   <si>
     <t>Queenstown Harbor — Entitled-Lot (Capital-Light) Development Model</t>
   </si>
@@ -218,7 +218,19 @@
     <t xml:space="preserve">    of which JAL (~1/3 of dev co)</t>
   </si>
   <si>
-    <t>sweat equity — separate from any placement fee or co-invest; + $15K/mo retainer</t>
+    <t>the carry — sweat equity; separate from any placement fee or co-invest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    + JAL retainer ($15K/mo × ~36 mo)</t>
+  </si>
+  <si>
+    <t>a floor during the engagement (a deal cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    = JAL all-in (illustrative)</t>
+  </si>
+  <si>
+    <t>carry + retainer on the Queenstown base case</t>
   </si>
   <si>
     <t>PROJECT CASH FLOW  (revenue × phasing − cost × phasing)</t>
@@ -1236,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1772,329 +1784,359 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="10">
+        <f>540000</f>
+        <v>540000</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+    </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="19" t="s">
+      <c r="A46" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="B46" s="14">
+        <f>B44+B45</f>
+        <v>2925333.333333333</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="B49" s="19" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="C49" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="20">
-        <v>0</v>
-      </c>
-      <c r="C48" s="20">
-        <v>0</v>
-      </c>
-      <c r="D48" s="20">
-        <v>0.25</v>
-      </c>
-      <c r="E48" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="F48" s="20">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="D49" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="C49" s="20">
-        <v>0.45</v>
-      </c>
-      <c r="D49" s="20">
-        <v>0.18</v>
-      </c>
-      <c r="E49" s="20">
-        <v>0.07</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0</v>
+      <c r="E49" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="21">
-        <f>$B$28*B48</f>
+        <v>80</v>
+      </c>
+      <c r="B50" s="20">
         <v>0</v>
       </c>
-      <c r="C50" s="21">
-        <f>$B$28*C48</f>
+      <c r="C50" s="20">
         <v>0</v>
       </c>
-      <c r="D50" s="21">
-        <f>$B$28*D48</f>
-        <v>4900000</v>
-      </c>
-      <c r="E50" s="21">
-        <f>$B$28*E48</f>
-        <v>7840000</v>
-      </c>
-      <c r="F50" s="21">
-        <f>$B$28*F48</f>
-        <v>6860000</v>
+      <c r="D50" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="E50" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="F50" s="20">
+        <v>0.35</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B51" s="21">
-        <f>-$B$35*B49</f>
+        <v>81</v>
+      </c>
+      <c r="B51" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="C51" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="D51" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="E51" s="20">
+        <v>0.07</v>
+      </c>
+      <c r="F51" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="21">
+        <f>$B$28*B50</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="21">
+        <f>$B$28*C50</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="21">
+        <f>$B$28*D50</f>
+        <v>4900000</v>
+      </c>
+      <c r="E52" s="21">
+        <f>$B$28*E50</f>
+        <v>7840000</v>
+      </c>
+      <c r="F52" s="21">
+        <f>$B$28*F50</f>
+        <v>6860000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="21">
+        <f>-$B$35*B51</f>
         <v>-1586400</v>
       </c>
-      <c r="C51" s="21">
-        <f>-$B$35*C49</f>
+      <c r="C53" s="21">
+        <f>-$B$35*C51</f>
         <v>-2379600</v>
       </c>
-      <c r="D51" s="21">
-        <f>-$B$35*D49</f>
+      <c r="D53" s="21">
+        <f>-$B$35*D51</f>
         <v>-951840</v>
       </c>
-      <c r="E51" s="21">
-        <f>-$B$35*E49</f>
+      <c r="E53" s="21">
+        <f>-$B$35*E51</f>
         <v>-370160.00000000006</v>
       </c>
-      <c r="F51" s="21">
-        <f>-$B$35*F49</f>
+      <c r="F53" s="21">
+        <f>-$B$35*F51</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="14">
-        <f>B50+B51</f>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="14">
+        <f>B52+B53</f>
         <v>-1586400</v>
       </c>
-      <c r="C52" s="14">
-        <f>C50+C51</f>
+      <c r="C54" s="14">
+        <f>C52+C53</f>
         <v>-2379600</v>
       </c>
-      <c r="D52" s="14">
-        <f>D50+D51</f>
+      <c r="D54" s="14">
+        <f>D52+D53</f>
         <v>3948160</v>
       </c>
-      <c r="E52" s="14">
-        <f>E50+E51</f>
+      <c r="E54" s="14">
+        <f>E52+E53</f>
         <v>7469840</v>
       </c>
-      <c r="F52" s="14">
-        <f>F50+F51</f>
+      <c r="F54" s="14">
+        <f>F52+F53</f>
         <v>6860000</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" s="22">
-        <f>IRR(B52:F52)</f>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="22">
+        <f>IRR(B54:F54)</f>
         <v>0.8626036987758889</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="24" t="s">
+      <c r="C55" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C56" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" s="14">
-        <v>19600000</v>
-      </c>
-      <c r="C57" s="21">
-        <v>42000000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" s="14">
-        <v>5288000</v>
-      </c>
-      <c r="C58" s="21">
-        <v>24636000</v>
+      <c r="C58" s="24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B59" s="14">
-        <v>14312000</v>
+        <v>19600000</v>
       </c>
       <c r="C59" s="21">
-        <v>17364000</v>
+        <v>42000000</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="14">
+        <v>5288000</v>
+      </c>
+      <c r="C60" s="21">
+        <v>24636000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" s="14">
+        <v>14312000</v>
+      </c>
+      <c r="C61" s="21">
+        <v>17364000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B62" s="17">
         <v>2.706505295007564</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C62" s="25">
         <v>0.7048222113979542</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-    </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="27" t="s">
+      <c r="A63" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="28" t="s">
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="29">
-        <v>8.104</v>
-      </c>
-      <c r="C65" s="29">
-        <v>10.238</v>
-      </c>
-      <c r="D65" s="29">
-        <v>12.372</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="28" t="s">
+      <c r="B66" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="29">
-        <v>11.596</v>
-      </c>
-      <c r="C66" s="30">
-        <v>14.312</v>
-      </c>
-      <c r="D66" s="29">
-        <v>17.028</v>
+      <c r="C66" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B67" s="29">
+        <v>8.104</v>
+      </c>
+      <c r="C67" s="29">
+        <v>10.238</v>
+      </c>
+      <c r="D67" s="29">
+        <v>12.372</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="29">
+        <v>11.596</v>
+      </c>
+      <c r="C68" s="30">
+        <v>14.312</v>
+      </c>
+      <c r="D68" s="29">
+        <v>17.028</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" s="29">
         <v>15.088</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C69" s="29">
         <v>18.386</v>
       </c>
-      <c r="D67" s="29">
+      <c r="D69" s="29">
         <v>21.684</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-    </row>
-    <row r="70" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+    </row>
+    <row r="72" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="38">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
@@ -2127,10 +2169,12 @@
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A72:F72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2150,7 +2194,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2160,7 +2204,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2180,13 +2224,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2194,13 +2238,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B6" s="10">
         <v>325000</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2208,13 +2252,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B7" s="10">
         <v>250</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2222,13 +2266,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B8" s="11">
         <v>0.62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2236,13 +2280,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B9" s="32">
         <v>1.6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2250,13 +2294,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B10" s="11">
         <v>0.31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2264,13 +2308,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B11" s="7">
         <v>16000</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2278,13 +2322,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B12" s="10">
         <v>550</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2292,13 +2336,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B13" s="10">
         <v>700</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -2306,13 +2350,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B14" s="11">
         <v>0.09</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -2320,13 +2364,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B15" s="10">
         <v>2000000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -2334,7 +2378,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B16" s="10">
         <v>3700000</v>
@@ -2342,13 +2386,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B17" s="11">
         <v>0.08</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -2356,7 +2400,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B18" s="11">
         <v>0.6</v>
@@ -2364,7 +2408,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B19" s="11">
         <v>0.07</v>
@@ -2372,7 +2416,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B20" s="11">
         <v>0.03</v>
@@ -2380,13 +2424,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B21" s="11">
         <v>0.5</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2394,13 +2438,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B22" s="11">
         <v>0.5</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -2408,7 +2452,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2418,14 +2462,14 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B25" s="10">
         <f>B5*B6</f>
         <v>32500000</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -2433,14 +2477,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B26" s="10">
         <f>B5*365*B7*B8</f>
         <v>5657500</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2448,14 +2492,14 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B27" s="10">
         <f>B26*B9</f>
         <v>9052000</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -2463,14 +2507,14 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B28" s="14">
         <f>B27*B10</f>
         <v>2806120</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -2478,7 +2522,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2488,14 +2532,14 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B31" s="10">
         <f>B11*B12</f>
         <v>8800000</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -2503,14 +2547,14 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B32" s="10">
         <f>B11*B13</f>
         <v>11200000</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -2518,14 +2562,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B33" s="14">
         <f>B32*B14</f>
         <v>1008000</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2533,7 +2577,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2543,14 +2587,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B36" s="16">
         <f>B25+B31+B15+B16</f>
         <v>47000000</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -2558,14 +2602,14 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B37" s="16">
         <f>B28+B33</f>
         <v>3814120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -2573,14 +2617,14 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B38" s="11">
         <f>B37/B36</f>
         <v>0.08115148936170213</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -2588,14 +2632,14 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B39" s="10">
         <f>B36*B18</f>
         <v>28200000</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -2603,14 +2647,14 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B40" s="10">
         <f>B36-B39</f>
         <v>18800000</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
@@ -2618,14 +2662,14 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B41" s="10">
         <f>B37-B39*B19</f>
         <v>1840119.9999999998</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -2633,14 +2677,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B42" s="11">
         <f>B41/B40</f>
         <v>0.09787872340425531</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2648,7 +2692,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2658,14 +2702,14 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B45" s="10">
         <f>B37*(1+B20)^4</f>
         <v>4292825.6623972</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
@@ -2673,14 +2717,14 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B46" s="10">
         <f>B45/B17</f>
         <v>53660320.779965</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
@@ -2688,14 +2732,14 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B47" s="10">
         <f>B46-B39</f>
         <v>25460320.779965</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -2703,7 +2747,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2713,7 +2757,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B50" s="21">
         <f>-B40*B21</f>
@@ -2722,7 +2766,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B51" s="21">
         <f>-B40*(1-B21)</f>
@@ -2731,7 +2775,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B52" s="21">
         <f>B41*B22</f>
@@ -2740,7 +2784,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B53" s="21">
         <f>B41</f>
@@ -2749,7 +2793,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B54" s="21">
         <f>B41*(1+B20)</f>
@@ -2758,7 +2802,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B55" s="21">
         <f>B41*(1+B20)^2</f>
@@ -2767,7 +2811,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B56" s="21">
         <f>B41*(1+B20)^3</f>
@@ -2776,7 +2820,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B57" s="21">
         <f>B41*(1+B20)^4+B47</f>
@@ -2785,14 +2829,14 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B58" s="17">
         <f>SUM(B52:B57)/-(B50+B51)</f>
         <v>1.9228631790777764</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -2800,14 +2844,14 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B59" s="22">
         <f>IRR(B50:B57)</f>
         <v>0.12039129900378642</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -2815,7 +2859,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2825,13 +2869,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B62" s="11">
         <v>0.22</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -2839,14 +2883,14 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B63" s="14">
         <f>B37*(1+B62)</f>
         <v>4653226.399999999</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -2854,13 +2898,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B64" s="11">
         <v>0.075</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -2868,13 +2912,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B65" s="11">
         <v>0.65</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -2882,13 +2926,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B66" s="11">
         <v>0.4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -2896,14 +2940,14 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B67" s="11">
         <f>B63/B36</f>
         <v>0.09900481702127659</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -2911,14 +2955,14 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B68" s="10">
         <f>B63/B64</f>
         <v>62043018.666666664</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -2926,14 +2970,14 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B69" s="10">
         <f>B36*B65</f>
         <v>30550000</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
@@ -2941,14 +2985,14 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B70" s="10">
         <f>B36-B69</f>
         <v>16450000</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
@@ -2956,14 +3000,14 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B71" s="10">
         <f>B63-B69*B19</f>
         <v>2514726.3999999994</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -2971,14 +3015,14 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B72" s="10">
         <f>B68-B69</f>
         <v>31493018.666666664</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
@@ -2986,7 +3030,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2996,7 +3040,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B75" s="21">
         <f>-B70*B21</f>
@@ -3005,7 +3049,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B76" s="21">
         <f>-B70*(1-B21)</f>
@@ -3014,7 +3058,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B77" s="21">
         <f>B71*B66</f>
@@ -3023,7 +3067,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B78" s="21">
         <f>B71</f>
@@ -3032,7 +3076,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B79" s="21">
         <f>B71+B72</f>
@@ -3041,14 +3085,14 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B80" s="17">
         <f>SUM(B77:B79)/-(B75+B76)</f>
         <v>2.281359393718338</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -3056,14 +3100,14 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B81" s="22">
         <f>IRR(B75:B79)</f>
         <v>0.27563551751308235</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -3071,7 +3115,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3081,7 +3125,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B84" s="33">
         <v>0.07</v>
@@ -3098,7 +3142,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B85" s="34">
         <v>0.2413590494653527</v>
@@ -3115,7 +3159,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B86" s="34">
         <v>0.3166711576166231</v>
@@ -3132,7 +3176,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="28" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B87" s="34">
         <v>0.3879656267349022</v>
@@ -3149,7 +3193,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -3159,7 +3203,7 @@
     </row>
     <row r="90" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="31" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B90" s="31"/>
       <c r="C90" s="31"/>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -119,7 +119,7 @@
     <t>JAL share of the dev co</t>
   </si>
   <si>
-    <t>sweat equity — ~1/3 of the dev-co 50% (~17% of profit)</t>
+    <t>sweat equity — 30% of the dev-co 50% (~15% of profit)</t>
   </si>
   <si>
     <t>DEVELOPABLE LAND  →  ENTITLED LOTS</t>
@@ -215,7 +215,7 @@
     <t>Accountable Equity / Capital H6 · Bob · JAL · partners</t>
   </si>
   <si>
-    <t xml:space="preserve">    of which JAL (~1/3 of dev co)</t>
+    <t xml:space="preserve">    of which JAL (30% of dev co)</t>
   </si>
   <si>
     <t>the carry — sweat equity; separate from any placement fee or co-invest</t>
@@ -1510,7 +1510,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="11">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>35</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B44" s="10">
         <f>B43*B21</f>
-        <v>2385333.333333333</v>
+        <v>2146800</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>68</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B46" s="14">
         <f>B44+B45</f>
-        <v>2925333.333333333</v>
+        <v>2686800</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>72</v>

--- a/JAL_Queenstown_Harbor_Model.xlsx
+++ b/JAL_Queenstown_Harbor_Model.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Entitled-Lot Model" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Phase 2 — Hospitality" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
   <si>
     <t>Queenstown Harbor — Entitled-Lot (Capital-Light) Development Model</t>
   </si>
@@ -321,354 +320,6 @@
   </si>
   <si>
     <t>Illustrative and for discussion only. Capital-light entitled-lot basis: we fund only the soft costs to entitle the land and sell entitled lots; the builder funds the horizontal. Costs repaid first, then a straight 50/50 (no pref, no promote). The entitled-lot price is the key assumption — confirm against builder bids in diligence.</t>
-  </si>
-  <si>
-    <t>Queenstown Harbor — Phase 2: Hospitality (Hotel + Restaurants)</t>
-  </si>
-  <si>
-    <t>Hotel is a REQUIRED component (per Bob). VIVÂMEE-led resort; JAL leads capital formation.  ·  Dynamic.  ·  ILLUSTRATIVE.</t>
-  </si>
-  <si>
-    <t>Hotel — keys</t>
-  </si>
-  <si>
-    <t>boutique resort lodge</t>
-  </si>
-  <si>
-    <t>Hotel — cost / key ($)</t>
-  </si>
-  <si>
-    <t>HVS 2025: select ~$223K, full-service ~$409K</t>
-  </si>
-  <si>
-    <t>Hotel — ADR ($)</t>
-  </si>
-  <si>
-    <t>upscale Eastern Shore resort (weddings / golf)</t>
-  </si>
-  <si>
-    <t>Hotel — stabilized occupancy</t>
-  </si>
-  <si>
-    <t>leisure / resort</t>
-  </si>
-  <si>
-    <t>Hotel — total-revenue multiple (x rooms)</t>
-  </si>
-  <si>
-    <t>+ F&amp;B, banquets, spa</t>
-  </si>
-  <si>
-    <t>Hotel — NOI margin</t>
-  </si>
-  <si>
-    <t>stabilized</t>
-  </si>
-  <si>
-    <t>Restaurants — GLA (SF)</t>
-  </si>
-  <si>
-    <t>a suite of destination restaurants</t>
-  </si>
-  <si>
-    <t>Restaurants — build cost / SF ($)</t>
-  </si>
-  <si>
-    <t>full-service ~$555/SF</t>
-  </si>
-  <si>
-    <t>Restaurants — sales / SF ($)</t>
-  </si>
-  <si>
-    <t>upscale destination dining</t>
-  </si>
-  <si>
-    <t>Restaurants — NOI (% of sales)</t>
-  </si>
-  <si>
-    <t>rent / operating contribution</t>
-  </si>
-  <si>
-    <t>Land — hospitality parcel ($)</t>
-  </si>
-  <si>
-    <t>contributed by Capital H6</t>
-  </si>
-  <si>
-    <t>Soft / FF&amp;E / pre-opening ($)</t>
-  </si>
-  <si>
-    <t>Exit cap rate (hold case)</t>
-  </si>
-  <si>
-    <t>hotel cap ~8% (2025)</t>
-  </si>
-  <si>
-    <t>Construction loan (% of cost)</t>
-  </si>
-  <si>
-    <t>Loan interest rate</t>
-  </si>
-  <si>
-    <t>NOI growth / yr</t>
-  </si>
-  <si>
-    <t>Equity drawn — Year 0 (balance Yr 1)</t>
-  </si>
-  <si>
-    <t>construction equity timing</t>
-  </si>
-  <si>
-    <t>First operating year ramp (hold)</t>
-  </si>
-  <si>
-    <t>Yr 2 opens partway through</t>
-  </si>
-  <si>
-    <t>HOTEL  (required component)</t>
-  </si>
-  <si>
-    <t>Hotel development cost</t>
-  </si>
-  <si>
-    <t>keys × cost/key</t>
-  </si>
-  <si>
-    <t>Room revenue</t>
-  </si>
-  <si>
-    <t>keys × 365 × ADR × occ</t>
-  </si>
-  <si>
-    <t>Total hotel revenue</t>
-  </si>
-  <si>
-    <t>× revenue multiple</t>
-  </si>
-  <si>
-    <t>Hotel NOI (stabilized)</t>
-  </si>
-  <si>
-    <t>× NOI margin</t>
-  </si>
-  <si>
-    <t>RESTAURANTS  (a suite of nice restaurants)</t>
-  </si>
-  <si>
-    <t>Restaurant development cost</t>
-  </si>
-  <si>
-    <t>SF × cost/SF</t>
-  </si>
-  <si>
-    <t>Restaurant sales</t>
-  </si>
-  <si>
-    <t>SF × sales/SF</t>
-  </si>
-  <si>
-    <t>Restaurant NOI (to owner)</t>
-  </si>
-  <si>
-    <t>TOTAL PROJECT  -&gt;  STABILIZED</t>
-  </si>
-  <si>
-    <t>Total project cost</t>
-  </si>
-  <si>
-    <t>hotel + restaurants + land + soft</t>
-  </si>
-  <si>
-    <t>Stabilized NOI</t>
-  </si>
-  <si>
-    <t>hotel + restaurant NOI</t>
-  </si>
-  <si>
-    <t>Yield on cost</t>
-  </si>
-  <si>
-    <t>NOI / cost</t>
-  </si>
-  <si>
-    <t>Construction loan</t>
-  </si>
-  <si>
-    <t>% LTC</t>
-  </si>
-  <si>
-    <t>Equity (land + cash)</t>
-  </si>
-  <si>
-    <t>cost − loan</t>
-  </si>
-  <si>
-    <t>Stabilized levered cash flow</t>
-  </si>
-  <si>
-    <t>NOI − loan interest</t>
-  </si>
-  <si>
-    <t>Cash-on-cash (stabilized, levered)</t>
-  </si>
-  <si>
-    <t>stabilized levered CF / equity</t>
-  </si>
-  <si>
-    <t>EXIT  (hold case — sell at exit cap)</t>
-  </si>
-  <si>
-    <t>Exit-year NOI (+3%/yr × 4)</t>
-  </si>
-  <si>
-    <t>stabilized × growth</t>
-  </si>
-  <si>
-    <t>Exit value (@ exit cap)</t>
-  </si>
-  <si>
-    <t>exit-year NOI / cap</t>
-  </si>
-  <si>
-    <t>Exit equity (value − loan)</t>
-  </si>
-  <si>
-    <t>net of loan</t>
-  </si>
-  <si>
-    <t>HOLD-CASE EQUITY CASH FLOW  (Yr 0–7, levered $) &amp; RETURNS</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 0</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 1</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 2</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 3</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 4</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 5</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 6</t>
-  </si>
-  <si>
-    <t>Equity CF — Year 7</t>
-  </si>
-  <si>
-    <t>Equity multiple (7-yr hold)</t>
-  </si>
-  <si>
-    <t>distributions / equity</t>
-  </si>
-  <si>
-    <t>Project IRR (levered, 7-yr hold)</t>
-  </si>
-  <si>
-    <t>income / hold — develops to ~cost</t>
-  </si>
-  <si>
-    <t>BUILD-TO-CORE CASE  (recap / sell at stabilization — path to mid–high 20s IRR)</t>
-  </si>
-  <si>
-    <t>NOI uplift — premium execution</t>
-  </si>
-  <si>
-    <t>VIVÂMEE experiential: ADR ~$275, occ ~63%, strong F&amp;B / events</t>
-  </si>
-  <si>
-    <t>Premium stabilized NOI</t>
-  </si>
-  <si>
-    <t>base NOI × (1 + uplift)</t>
-  </si>
-  <si>
-    <t>Exit cap (build-to-core)</t>
-  </si>
-  <si>
-    <t>trophy / experiential resort</t>
-  </si>
-  <si>
-    <t>Leverage (% of cost)</t>
-  </si>
-  <si>
-    <t>construction loan</t>
-  </si>
-  <si>
-    <t>First operating year ramp (b-t-c)</t>
-  </si>
-  <si>
-    <t>Yield on cost (premium)</t>
-  </si>
-  <si>
-    <t>premium NOI / cost — vs 7.5% exit = the spread</t>
-  </si>
-  <si>
-    <t>Recap / sale value (~Yr 4)</t>
-  </si>
-  <si>
-    <t>premium NOI / exit cap</t>
-  </si>
-  <si>
-    <t>Loan</t>
-  </si>
-  <si>
-    <t>% of cost</t>
-  </si>
-  <si>
-    <t>Equity</t>
-  </si>
-  <si>
-    <t>Premium stabilized levered cash flow</t>
-  </si>
-  <si>
-    <t>premium NOI − loan interest</t>
-  </si>
-  <si>
-    <t>at recap / sale</t>
-  </si>
-  <si>
-    <t>BUILD-TO-CORE EQUITY CASH FLOW  (Yr 0–4, levered $) &amp; RETURNS</t>
-  </si>
-  <si>
-    <t>Equity multiple (build-to-core)</t>
-  </si>
-  <si>
-    <t>distributions / equity, ~4-yr</t>
-  </si>
-  <si>
-    <t>Project IRR (build-to-core, ~4-yr)</t>
-  </si>
-  <si>
-    <t>recap / sell at stabilization</t>
-  </si>
-  <si>
-    <t>BUILD-TO-CORE IRR SENSITIVITY  (stabilized NOI  ×  exit cap)</t>
-  </si>
-  <si>
-    <t>Stabilized NOI  /  exit cap</t>
-  </si>
-  <si>
-    <t>$4.2M NOI</t>
-  </si>
-  <si>
-    <t>$4.65M NOI (base)</t>
-  </si>
-  <si>
-    <t>$5.15M NOI</t>
-  </si>
-  <si>
-    <t>Build-to-core project IRR at 65% LTC, recap at stabilization (~Yr 4). Base = $4.65M NOI / 7.5% cap (highlighted). Each cell re-runs the engine.</t>
-  </si>
-  <si>
-    <t>Illustrative. The hotel is a required component (per Bob); at Renault the plan is +100–200 rooms. Hospitality develops to ~cost (income/hold ~12% IRR) unless you build to core and recap at stabilization (~28%). VIVÂMEE operates; JAL leads capital formation. The resort also lifts the lot values. Subject to confirmation.</t>
   </si>
 </sst>
 </file>
@@ -814,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -896,18 +547,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2179,1091 +1818,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="7">
-        <v>100</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="10">
-        <v>325000</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="10">
-        <v>250</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="11">
-        <v>0.62</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="32">
-        <v>1.6</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="11">
-        <v>0.31</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="7">
-        <v>16000</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="10">
-        <v>550</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="10">
-        <v>700</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="11">
-        <v>0.09</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="10">
-        <v>3700000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="11">
-        <v>0.08</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="11">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="11">
-        <v>0.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="11">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B21" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="10">
-        <f>B5*B6</f>
-        <v>32500000</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="10">
-        <f>B5*365*B7*B8</f>
-        <v>5657500</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="10">
-        <f>B26*B9</f>
-        <v>9052000</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="14">
-        <f>B27*B10</f>
-        <v>2806120</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="10">
-        <f>B11*B12</f>
-        <v>8800000</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="10">
-        <f>B11*B13</f>
-        <v>11200000</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="14">
-        <f>B32*B14</f>
-        <v>1008000</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="16">
-        <f>B25+B31+B15+B16</f>
-        <v>47000000</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B37" s="16">
-        <f>B28+B33</f>
-        <v>3814120</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="11">
-        <f>B37/B36</f>
-        <v>0.08115148936170213</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B39" s="10">
-        <f>B36*B18</f>
-        <v>28200000</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B40" s="10">
-        <f>B36-B39</f>
-        <v>18800000</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B41" s="10">
-        <f>B37-B39*B19</f>
-        <v>1840119.9999999998</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B42" s="11">
-        <f>B41/B40</f>
-        <v>0.09787872340425531</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B45" s="10">
-        <f>B37*(1+B20)^4</f>
-        <v>4292825.6623972</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B46" s="10">
-        <f>B45/B17</f>
-        <v>53660320.779965</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="10">
-        <f>B46-B39</f>
-        <v>25460320.779965</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B50" s="21">
-        <f>-B40*B21</f>
-        <v>-9400000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B51" s="21">
-        <f>-B40*(1-B21)</f>
-        <v>-9400000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B52" s="21">
-        <f>B41*B22</f>
-        <v>920059.9999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B53" s="21">
-        <f>B41</f>
-        <v>1840119.9999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B54" s="21">
-        <f>B41*(1+B20)</f>
-        <v>1895323.5999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B55" s="21">
-        <f>B41*(1+B20)^2</f>
-        <v>1952183.3079999997</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B56" s="21">
-        <f>B41*(1+B20)^3</f>
-        <v>2010748.8072399998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B57" s="21">
-        <f>B41*(1+B20)^4+B47</f>
-        <v>27531392.051422197</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B58" s="17">
-        <f>SUM(B52:B57)/-(B50+B51)</f>
-        <v>1.9228631790777764</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" s="22">
-        <f>IRR(B50:B57)</f>
-        <v>0.12039129900378642</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B62" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B63" s="14">
-        <f>B37*(1+B62)</f>
-        <v>4653226.399999999</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B64" s="11">
-        <v>0.075</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B65" s="11">
-        <v>0.65</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B66" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B67" s="11">
-        <f>B63/B36</f>
-        <v>0.09900481702127659</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B68" s="10">
-        <f>B63/B64</f>
-        <v>62043018.666666664</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B69" s="10">
-        <f>B36*B65</f>
-        <v>30550000</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B70" s="10">
-        <f>B36-B69</f>
-        <v>16450000</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B71" s="10">
-        <f>B63-B69*B19</f>
-        <v>2514726.3999999994</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B72" s="10">
-        <f>B68-B69</f>
-        <v>31493018.666666664</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B75" s="21">
-        <f>-B70*B21</f>
-        <v>-8225000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B76" s="21">
-        <f>-B70*(1-B21)</f>
-        <v>-8225000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B77" s="21">
-        <f>B71*B66</f>
-        <v>1005890.5599999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B78" s="21">
-        <f>B71</f>
-        <v>2514726.3999999994</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B79" s="21">
-        <f>B71+B72</f>
-        <v>34007745.06666666</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B80" s="17">
-        <f>SUM(B77:B79)/-(B75+B76)</f>
-        <v>2.281359393718338</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B81" s="22">
-        <f>IRR(B75:B79)</f>
-        <v>0.27563551751308235</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B84" s="33">
-        <v>0.07</v>
-      </c>
-      <c r="C84" s="33">
-        <v>0.075</v>
-      </c>
-      <c r="D84" s="33">
-        <v>0.08</v>
-      </c>
-      <c r="E84" s="33">
-        <v>0.085</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="B85" s="34">
-        <v>0.2413590494653527</v>
-      </c>
-      <c r="C85" s="34">
-        <v>0.1981010805160578</v>
-      </c>
-      <c r="D85" s="34">
-        <v>0.15643182900562425</v>
-      </c>
-      <c r="E85" s="34">
-        <v>0.11594756701498155</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="B86" s="34">
-        <v>0.3166711576166231</v>
-      </c>
-      <c r="C86" s="35">
-        <v>0.27563551751308235</v>
-      </c>
-      <c r="D86" s="34">
-        <v>0.2365089547947662</v>
-      </c>
-      <c r="E86" s="34">
-        <v>0.1989302587607228</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="B87" s="34">
-        <v>0.3879656267349022</v>
-      </c>
-      <c r="C87" s="34">
-        <v>0.3484741336946878</v>
-      </c>
-      <c r="D87" s="34">
-        <v>0.31109801406577653</v>
-      </c>
-      <c r="E87" s="34">
-        <v>0.2754915069098355</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="90" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="B90" s="31"/>
-      <c r="C90" s="31"/>
-      <c r="D90" s="31"/>
-      <c r="E90" s="31"/>
-      <c r="F90" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="C66:F66"/>
-    <mergeCell ref="C67:F67"/>
-    <mergeCell ref="C68:F68"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A90:F90"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>